--- a/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
+++ b/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="488">
-  <si>
-    <t>ProofLoop タスクシート 2026-08 → 2027-01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="521">
+  <si>
+    <t>ProofLoop タスクシート 2026-08 → 2027-01（最終更新 2026-08-11）</t>
   </si>
   <si>
     <t>← バーは「開始」「終了」列の数字で動く（1＝8月前半 … 12＝1月後半）</t>
@@ -161,22 +161,31 @@
     <t>承認済み設計書</t>
   </si>
   <si>
+    <t>✅ 完了</t>
+  </si>
+  <si>
     <t>B2</t>
   </si>
   <si>
     <t>claim動線の実装・テスト・本番反映</t>
   </si>
   <si>
-    <t>掲載ページから団体が自分で引き取れる</t>
+    <t>掲載ページから団体が自分で引き取れる（028〜034 適用済み）</t>
   </si>
   <si>
     <t>B3</t>
   </si>
   <si>
-    <t>claimトークンの一括発行（2,354件）</t>
-  </si>
-  <si>
-    <t>団体別のclaim URL一覧</t>
+    <t>claimトークンの一括発行（2,222件）</t>
+  </si>
+  <si>
+    <t>B2,B18,B19,B20</t>
+  </si>
+  <si>
+    <t>団体別のclaim URL一覧。※発行前に B18〜B21 を終える</t>
+  </si>
+  <si>
+    <t>進行中</t>
   </si>
   <si>
     <t>B4</t>
@@ -197,10 +206,7 @@
     <t>優先順位付きリストの生成・バッチ分割</t>
   </si>
   <si>
-    <t>団体_声かけ優先順位.csv（2,354件・バッチ1〜6）</t>
-  </si>
-  <si>
-    <t>✅ 完了</t>
+    <t>団体_声かけ優先順位.csv（2,222件・バッチ1〜6）</t>
   </si>
   <si>
     <t>B6</t>
@@ -323,6 +329,42 @@
     <t>要望リストと次期計画</t>
   </si>
   <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>【公開前ゲート】claimトークンがGA4に送信されるのを止める</t>
+  </si>
+  <si>
+    <t>/claim・/invite のURLを丸めてから送信。**発行前に必須**</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>【公開前ゲート】運営が単独で剥奪できるUI（revoke_claim）</t>
+  </si>
+  <si>
+    <t>/admin/claims に「発行の取消」。却下時の復元も同時に直す</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>【公開前ゲート】新規登録のあと claim へ戻す導線</t>
+  </si>
+  <si>
+    <t>/signup から元のclaim URLへ復帰できる（設計§6.1）</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>【公開前ゲート】先行申請で締め出された団体の救済</t>
+  </si>
+  <si>
+    <t>再発行の手順書 or /admin/claims に再発行ボタン</t>
+  </si>
+  <si>
     <t>C1</t>
   </si>
   <si>
@@ -503,10 +545,10 @@
     <t>D3</t>
   </si>
   <si>
-    <t>middleware.ts でサーバーサイド認証ゲート（リスクS1）</t>
-  </si>
-  <si>
-    <t>/admin をサーバー側で保護</t>
+    <t>middleware.ts でサーバーサイド認証ゲート（リスクS1・Basic認証）</t>
+  </si>
+  <si>
+    <t>/admin をサーバー側で保護。401を本番で確認</t>
   </si>
   <si>
     <t>D4</t>
@@ -536,6 +578,54 @@
     <t>新機能は原則作らない</t>
   </si>
   <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>重いクエリの棚卸しと軽量化（索引7本・トップ/検索）</t>
+  </si>
+  <si>
+    <t>全件走査を除去。閲覧数取得が49ブロック→7バッファ</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>Supabase コンピュート増強（NANO→MICRO・障害復旧）</t>
+  </si>
+  <si>
+    <t>本番停止からの復旧と再発防止。追加費用なし</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>★claimオーナーが応募（ATS・応募DM）に到達できない</t>
+  </si>
+  <si>
+    <t>オーナー判断→Claude</t>
+  </si>
+  <si>
+    <t>applications/application_messages のRLSをメンバー起点へ</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>/organizations/[id] の ISR 導入（流入時の負荷対策）</t>
+  </si>
+  <si>
+    <t>1アクセス毎のサーバ処理を減らす。claim_status の鮮度と要トレードオフ</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>Reactコンポーネントのテスト基盤（RTL）導入</t>
+  </si>
+  <si>
+    <t>effectの解決順序・認可リダイレクトを回帰で守る</t>
+  </si>
+  <si>
     <t>E1</t>
   </si>
   <si>
@@ -683,6 +773,15 @@
     <t>種別振り分けと一次対応の設計へ</t>
   </si>
   <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>/admin の Basic認証用 環境変数を Vercel に設定</t>
+  </si>
+  <si>
+    <t>Production/Preview に設定。本番で401を確認</t>
+  </si>
+  <si>
     <t>【使い方】「開始」「終了」列に 1〜12 のコマ番号を入れるとバーが動く。1＝2026-08前半、12＝2027-01後半。</t>
   </si>
   <si>
@@ -944,7 +1043,7 @@
     <t>団体の声かけ優先順位（B4・B5 の成果物）</t>
   </si>
   <si>
-    <t>全件リストは 団体_声かけ優先順位.csv（2,354件・バッチ1〜6付き）。このシートは考え方と上位100件の抜粋。</t>
+    <t>全件リストは 団体_声かけ優先順位.csv（2,222件・バッチ1〜6付き）。このシートは考え方と上位100件の抜粋。</t>
   </si>
   <si>
     <t>■ スコアの考え方（100点満点）</t>
@@ -998,15 +1097,15 @@
     <t>第1バッチ</t>
   </si>
   <si>
+    <t>早稲田大学</t>
+  </si>
+  <si>
+    <t>第2バッチ</t>
+  </si>
+  <si>
     <t>慶應義塾大学</t>
   </si>
   <si>
-    <t>第2バッチ</t>
-  </si>
-  <si>
-    <t>早稲田大学</t>
-  </si>
-  <si>
     <t>第3バッチ</t>
   </si>
   <si>
@@ -1028,24 +1127,24 @@
     <t>第6バッチ</t>
   </si>
   <si>
+    <t>大阪大学</t>
+  </si>
+  <si>
+    <t>合計</t>
+  </si>
+  <si>
     <t>一橋大学</t>
   </si>
   <si>
-    <t>合計</t>
-  </si>
-  <si>
-    <t>大阪大学</t>
-  </si>
-  <si>
     <t>北海道大学</t>
   </si>
   <si>
+    <t>名古屋大学</t>
+  </si>
+  <si>
     <t>九州大学</t>
   </si>
   <si>
-    <t>名古屋大学</t>
-  </si>
-  <si>
     <t>東北大学</t>
   </si>
   <si>
@@ -1076,325 +1175,325 @@
     <t>スコア</t>
   </si>
   <si>
+    <t>理工展連絡会</t>
+  </si>
+  <si>
+    <t>イベント・企画（インカレ・学園祭等）</t>
+  </si>
+  <si>
+    <t>X/Instagram/Web</t>
+  </si>
+  <si>
     <t>硬式庭球部（薬学部）</t>
   </si>
   <si>
     <t>運動系（スポーツ・アウトドア）</t>
   </si>
   <si>
-    <t>X/Instagram/Web</t>
-  </si>
-  <si>
-    <t>理工展連絡会</t>
-  </si>
-  <si>
-    <t>イベント・企画（インカレ・学園祭等）</t>
-  </si>
-  <si>
     <t>Sophia Sustainable Coffee Movement (SSCM)</t>
   </si>
   <si>
     <t>趣味・その他</t>
   </si>
   <si>
+    <t>ローバース</t>
+  </si>
+  <si>
     <t>ゴルフ部（理工学部）</t>
   </si>
   <si>
-    <t>ローバース</t>
-  </si>
-  <si>
     <t>硬式庭球同好会フリーク</t>
   </si>
   <si>
     <t>東京大学工学部モーター同好会</t>
   </si>
   <si>
+    <t>aka Wa.Se.Da.</t>
+  </si>
+  <si>
     <t>体育会ハンドボール部</t>
   </si>
   <si>
     <t>アルメリア・ローン・テニスクラブ</t>
   </si>
   <si>
-    <t>aka Wa.Se.Da.</t>
+    <t>アルティメット部</t>
   </si>
   <si>
     <t>端艇部</t>
   </si>
   <si>
-    <t>アルティメット部</t>
-  </si>
-  <si>
     <t>男子バレーボール部</t>
   </si>
   <si>
+    <t>アメリカンフットボール部</t>
+  </si>
+  <si>
     <t>フィルハーモニーオーケストラ</t>
   </si>
   <si>
     <t>文化系（音楽・演劇・アート）</t>
   </si>
   <si>
-    <t>アメリカンフットボール部</t>
-  </si>
-  <si>
     <t>川内バドミントン同好会</t>
   </si>
   <si>
+    <t>バドミントン同好会</t>
+  </si>
+  <si>
     <t>バドミントン愛好会</t>
   </si>
   <si>
-    <t>バドミントン同好会</t>
-  </si>
-  <si>
     <t>上南戦実行委員会</t>
   </si>
   <si>
     <t>不明</t>
   </si>
   <si>
+    <t>軽音サークルZETS</t>
+  </si>
+  <si>
     <t>陸上競技同好会</t>
   </si>
   <si>
-    <t>軽音サークルZETS</t>
-  </si>
-  <si>
     <t>弓術部</t>
   </si>
   <si>
+    <t>パディ・ゴルフクラブ</t>
+  </si>
+  <si>
     <t>ソフィア祭実行委員会</t>
   </si>
   <si>
+    <t>弓道同好会</t>
+  </si>
+  <si>
+    <t>環境サークルGECS</t>
+  </si>
+  <si>
+    <t>学術・研究（ゼミ・研究会・勉強会）</t>
+  </si>
+  <si>
+    <t>体育会弓道部</t>
+  </si>
+  <si>
+    <t>大学祭全学実行委員会</t>
+  </si>
+  <si>
     <t>ICU祭実行委員会</t>
   </si>
   <si>
-    <t>弓道同好会</t>
-  </si>
-  <si>
-    <t>パディ・ゴルフクラブ</t>
-  </si>
-  <si>
-    <t>体育会弓道部</t>
-  </si>
-  <si>
-    <t>環境サークルGECS</t>
-  </si>
-  <si>
-    <t>学術・研究（ゼミ・研究会・勉強会）</t>
-  </si>
-  <si>
-    <t>スポーツ愛好会卓球部</t>
-  </si>
-  <si>
-    <t>大学祭全学実行委員会</t>
+    <t>少林寺拳法部</t>
   </si>
   <si>
     <t>フォークソング部</t>
   </si>
   <si>
+    <t>早稲田大学フラッシュモ部</t>
+  </si>
+  <si>
+    <t>卓球部（理工学部）</t>
+  </si>
+  <si>
+    <t>ギター研究会</t>
+  </si>
+  <si>
+    <t>剣道部</t>
+  </si>
+  <si>
+    <t>山歩会</t>
+  </si>
+  <si>
     <t>上智大学資格取得サークル(SCC)</t>
   </si>
   <si>
     <t>Instagram/Web</t>
   </si>
   <si>
-    <t>ギター研究会</t>
-  </si>
-  <si>
-    <t>少林寺拳法部</t>
-  </si>
-  <si>
-    <t>山歩会</t>
-  </si>
-  <si>
-    <t>早稲田大学フラッシュモ部</t>
-  </si>
-  <si>
-    <t>剣道部</t>
-  </si>
-  <si>
-    <t>卓球部（理工学部）</t>
-  </si>
-  <si>
     <t>東京大学Diligent</t>
   </si>
   <si>
     <t>早大テニスクラブ</t>
   </si>
   <si>
+    <t>應援指導部</t>
+  </si>
+  <si>
+    <t>国際学生友好会(WIC)</t>
+  </si>
+  <si>
+    <t>国際交流・語学</t>
+  </si>
+  <si>
     <t>星空研究会</t>
   </si>
   <si>
-    <t>應援指導部</t>
-  </si>
-  <si>
-    <t>国際学生友好会(WIC)</t>
-  </si>
-  <si>
-    <t>国際交流・語学</t>
+    <t>バスケットボール部</t>
+  </si>
+  <si>
+    <t>オリエンテーリング部</t>
   </si>
   <si>
     <t>KODAIRA祭実行委員会</t>
   </si>
   <si>
-    <t>バスケットボール部</t>
-  </si>
-  <si>
-    <t>オリエンテーリング部</t>
+    <t>E.M.B.G.</t>
+  </si>
+  <si>
+    <t>洋弓部</t>
+  </si>
+  <si>
+    <t>英語部 (WESA)</t>
+  </si>
+  <si>
+    <t>X/Instagram/Web/LINE</t>
+  </si>
+  <si>
+    <t>Business Contest KING 実行委員会</t>
+  </si>
+  <si>
+    <t>躰道部</t>
+  </si>
+  <si>
+    <t>サイクリング部</t>
   </si>
   <si>
     <t>上智女子ラグビークラブ</t>
   </si>
   <si>
-    <t>E.M.B.G.</t>
-  </si>
-  <si>
-    <t>洋弓部</t>
-  </si>
-  <si>
-    <t>英語部 (WESA)</t>
-  </si>
-  <si>
-    <t>X/Instagram/Web/LINE</t>
-  </si>
-  <si>
-    <t>サイクリング部</t>
-  </si>
-  <si>
-    <t>Business Contest KING 実行委員会</t>
-  </si>
-  <si>
-    <t>躰道部</t>
+    <t>グリーンテニスクラブ</t>
   </si>
   <si>
     <t>ボディビル部</t>
   </si>
   <si>
+    <t>九球テニスクラブ</t>
+  </si>
+  <si>
+    <t>城北テニスクラブ</t>
+  </si>
+  <si>
     <t>上智大学ダイビングクラブ海洋生態研究会</t>
   </si>
   <si>
+    <t>叡風会</t>
+  </si>
+  <si>
+    <t>競走部(医学部)</t>
+  </si>
+  <si>
+    <t>大学祭中央実行委員会</t>
+  </si>
+  <si>
+    <t>一橋祭運営委員会</t>
+  </si>
+  <si>
+    <t>TEDxUTokyo実行委員会</t>
+  </si>
+  <si>
+    <t>早大フォーティラブ</t>
+  </si>
+  <si>
+    <t>競技ダンス部</t>
+  </si>
+  <si>
+    <t>スケート部</t>
+  </si>
+  <si>
+    <t>体育会女子グランドホッケー部</t>
+  </si>
+  <si>
     <t>アーチェリー部</t>
   </si>
   <si>
-    <t>グリーンテニスクラブ</t>
-  </si>
-  <si>
-    <t>九球テニスクラブ</t>
-  </si>
-  <si>
-    <t>叡風会</t>
-  </si>
-  <si>
-    <t>競走部(医学部)</t>
-  </si>
-  <si>
-    <t>城北テニスクラブ</t>
-  </si>
-  <si>
-    <t>体育会女子グランドホッケー部</t>
-  </si>
-  <si>
-    <t>一橋祭運営委員会</t>
-  </si>
-  <si>
-    <t>大学祭中央実行委員会</t>
-  </si>
-  <si>
-    <t>TEDxUTokyo実行委員会</t>
-  </si>
-  <si>
-    <t>競技ダンス部</t>
-  </si>
-  <si>
-    <t>早大フォーティラブ</t>
-  </si>
-  <si>
-    <t>スケート部</t>
-  </si>
-  <si>
-    <t>フェンシング部</t>
+    <t>空手道部</t>
+  </si>
+  <si>
+    <t>鉄道研究同好会</t>
+  </si>
+  <si>
+    <t>早稲田大学　下駄っぱーず</t>
+  </si>
+  <si>
+    <t>水泳部(医学部)</t>
+  </si>
+  <si>
+    <t>アニメーション研究会</t>
+  </si>
+  <si>
+    <t>民族舞踊研究会</t>
+  </si>
+  <si>
+    <t>卓球部</t>
+  </si>
+  <si>
+    <t>早稲田大学バレエサークル　Ｃiel</t>
   </si>
   <si>
     <t>体育会水泳部(竸泳・水球部門)</t>
   </si>
   <si>
-    <t>アニメーション研究会</t>
-  </si>
-  <si>
-    <t>空手道部</t>
-  </si>
-  <si>
-    <t>卓球部</t>
-  </si>
-  <si>
-    <t>水泳部(医学部)</t>
-  </si>
-  <si>
-    <t>早稲田大学　下駄っぱーず</t>
-  </si>
-  <si>
-    <t>民族舞踊研究会</t>
+    <t>東京大学文学研究会</t>
   </si>
   <si>
     <t>ソフトテニス部</t>
   </si>
   <si>
+    <t>山岳部</t>
+  </si>
+  <si>
+    <t>女子ラクロス部</t>
+  </si>
+  <si>
+    <t>SEIREN</t>
+  </si>
+  <si>
+    <t>クリケット部</t>
+  </si>
+  <si>
     <t>上智大学フランス語倶楽部</t>
   </si>
   <si>
-    <t>早稲田大学バレエサークル　Ｃiel</t>
-  </si>
-  <si>
-    <t>東京大学文学研究会</t>
-  </si>
-  <si>
-    <t>女子ラクロス部</t>
-  </si>
-  <si>
-    <t>山岳部</t>
-  </si>
-  <si>
-    <t>クリケット部</t>
-  </si>
-  <si>
-    <t>SEIREN</t>
+    <t>合気会合気道部</t>
+  </si>
+  <si>
+    <t>交響楽団</t>
+  </si>
+  <si>
+    <t>ホッケー部</t>
+  </si>
+  <si>
+    <t>日本拳法部</t>
+  </si>
+  <si>
+    <t>女子バスケットボール部</t>
+  </si>
+  <si>
+    <t>バレーボール同好会</t>
+  </si>
+  <si>
+    <t>東京大学ロースクールサッカー部</t>
+  </si>
+  <si>
+    <t>Street Corner Symphony</t>
   </si>
   <si>
     <t>体育会フィギュアスケート部クリスタロス</t>
   </si>
   <si>
-    <t>女子サッカー部（OFF-SIDES）</t>
-  </si>
-  <si>
-    <t>合気会合気道部</t>
-  </si>
-  <si>
-    <t>ホッケー部</t>
-  </si>
-  <si>
-    <t>バレーボール同好会</t>
-  </si>
-  <si>
-    <t>スキー部</t>
-  </si>
-  <si>
-    <t>日本拳法部</t>
-  </si>
-  <si>
-    <t>交響楽団</t>
-  </si>
-  <si>
     <t>Revolve</t>
   </si>
   <si>
-    <t>日本模擬国連四ツ谷研究会（よつけん）</t>
-  </si>
-  <si>
-    <t>東京大学ロースクールサッカー部</t>
-  </si>
-  <si>
-    <t>Street Corner Symphony</t>
+    <t>ソフトボール部</t>
   </si>
   <si>
     <t>体操部</t>
+  </si>
+  <si>
+    <t>早大ピアノの会</t>
+  </si>
+  <si>
+    <t>Accounting Academy</t>
   </si>
   <si>
     <t>このファイルの使い方</t>
@@ -2272,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U70"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2689,10 +2788,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="14">
-        <v>2</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
@@ -2709,13 +2808,13 @@
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>38</v>
@@ -2724,16 +2823,16 @@
         <v>43</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="14">
-        <v>3</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
@@ -2750,22 +2849,22 @@
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G13" s="14">
         <v>3</v>
@@ -2774,7 +2873,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
@@ -2791,13 +2890,13 @@
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>24</v>
@@ -2806,7 +2905,7 @@
         <v>25</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
@@ -2815,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -2832,22 +2931,22 @@
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
@@ -2856,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -2873,22 +2972,22 @@
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G16" s="14">
         <v>2</v>
@@ -2914,13 +3013,13 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>30</v>
@@ -2929,7 +3028,7 @@
         <v>25</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G17" s="14">
         <v>2</v>
@@ -2955,22 +3054,22 @@
     </row>
     <row r="18" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
@@ -2996,22 +3095,22 @@
     </row>
     <row r="19" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G19" s="14">
         <v>2</v>
@@ -3037,22 +3136,22 @@
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
@@ -3078,22 +3177,22 @@
     </row>
     <row r="21" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G21" s="14">
         <v>3</v>
@@ -3119,22 +3218,22 @@
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
@@ -3160,22 +3259,22 @@
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G23" s="14">
         <v>7</v>
@@ -3201,22 +3300,22 @@
     </row>
     <row r="24" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
         <v>9</v>
@@ -3242,22 +3341,22 @@
     </row>
     <row r="25" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G25" s="14">
         <v>11</v>
@@ -3283,22 +3382,22 @@
     </row>
     <row r="26" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G26" s="14">
         <v>3</v>
@@ -3324,22 +3423,22 @@
     </row>
     <row r="27" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D27" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>95</v>
-      </c>
       <c r="F27" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G27" s="14">
         <v>9</v>
@@ -3364,29 +3463,29 @@
       <c r="U27" s="15"/>
     </row>
     <row r="28" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="21" t="s">
+      <c r="A28" s="16" t="s">
         <v>104</v>
       </c>
+      <c r="B28" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>105</v>
+      </c>
       <c r="D28" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I28" s="14" t="s">
         <v>27</v>
@@ -3405,20 +3504,20 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>103</v>
+      <c r="A29" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>109</v>
@@ -3446,23 +3545,23 @@
       <c r="U29" s="15"/>
     </row>
     <row r="30" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>103</v>
+      <c r="B30" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>111</v>
       </c>
       <c r="D30" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
@@ -3487,23 +3586,23 @@
       <c r="U30" s="15"/>
     </row>
     <row r="31" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>115</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>116</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
@@ -3529,28 +3628,28 @@
     </row>
     <row r="32" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>117</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>103</v>
       </c>
       <c r="C32" s="21" t="s">
         <v>118</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>119</v>
       </c>
       <c r="G32" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" s="14" t="s">
         <v>27</v>
@@ -3573,25 +3672,25 @@
         <v>120</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>121</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
         <v>2</v>
-      </c>
-      <c r="H33" s="14">
-        <v>3</v>
       </c>
       <c r="I33" s="14" t="s">
         <v>27</v>
@@ -3611,28 +3710,28 @@
     </row>
     <row r="34" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G34" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" s="14" t="s">
         <v>27</v>
@@ -3652,28 +3751,28 @@
     </row>
     <row r="35" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I35" s="14" t="s">
         <v>27</v>
@@ -3693,28 +3792,28 @@
     </row>
     <row r="36" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>131</v>
+        <v>117</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G36" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H36" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I36" s="14" t="s">
         <v>27</v>
@@ -3734,28 +3833,28 @@
     </row>
     <row r="37" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H37" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I37" s="14" t="s">
         <v>27</v>
@@ -3775,28 +3874,28 @@
     </row>
     <row r="38" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G38" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H38" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I38" s="14" t="s">
         <v>27</v>
@@ -3816,28 +3915,28 @@
     </row>
     <row r="39" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G39" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H39" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I39" s="14" t="s">
         <v>27</v>
@@ -3857,28 +3956,28 @@
     </row>
     <row r="40" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G40" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H40" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I40" s="14" t="s">
         <v>27</v>
@@ -3898,28 +3997,28 @@
     </row>
     <row r="41" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G41" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H41" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I41" s="14" t="s">
         <v>27</v>
@@ -3939,28 +4038,28 @@
     </row>
     <row r="42" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G42" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H42" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I42" s="14" t="s">
         <v>27</v>
@@ -3980,28 +4079,28 @@
     </row>
     <row r="43" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G43" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H43" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I43" s="14" t="s">
         <v>27</v>
@@ -4020,29 +4119,29 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>155</v>
+      <c r="A44" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G44" s="14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H44" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I44" s="14" t="s">
         <v>27</v>
@@ -4061,29 +4160,29 @@
       <c r="U44" s="15"/>
     </row>
     <row r="45" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>155</v>
+      <c r="A45" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G45" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I45" s="14" t="s">
         <v>27</v>
@@ -4102,29 +4201,29 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>155</v>
+      <c r="A46" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G46" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H46" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I46" s="14" t="s">
         <v>27</v>
@@ -4143,29 +4242,29 @@
       <c r="U46" s="15"/>
     </row>
     <row r="47" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B47" s="23" t="s">
-        <v>155</v>
+      <c r="A47" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G47" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H47" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I47" s="14" t="s">
         <v>27</v>
@@ -4185,28 +4284,28 @@
     </row>
     <row r="48" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G48" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H48" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I48" s="14" t="s">
         <v>27</v>
@@ -4226,13 +4325,13 @@
     </row>
     <row r="49" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>38</v>
@@ -4241,13 +4340,13 @@
         <v>25</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G49" s="14">
+        <v>2</v>
+      </c>
+      <c r="H49" s="14">
         <v>3</v>
-      </c>
-      <c r="H49" s="14">
-        <v>12</v>
       </c>
       <c r="I49" s="14" t="s">
         <v>27</v>
@@ -4266,17 +4365,17 @@
       <c r="U49" s="15"/>
     </row>
     <row r="50" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B50" s="25" t="s">
-        <v>174</v>
+      <c r="A50" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>25</v>
@@ -4288,10 +4387,10 @@
         <v>1</v>
       </c>
       <c r="H50" s="14">
-        <v>2</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
@@ -4307,11 +4406,11 @@
       <c r="U50" s="15"/>
     </row>
     <row r="51" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
+      <c r="A51" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="25" t="s">
-        <v>174</v>
+      <c r="B51" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>179</v>
@@ -4320,16 +4419,16 @@
         <v>38</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>180</v>
       </c>
       <c r="G51" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I51" s="14" t="s">
         <v>27</v>
@@ -4348,11 +4447,11 @@
       <c r="U51" s="15"/>
     </row>
     <row r="52" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="24" t="s">
+      <c r="A52" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B52" s="25" t="s">
-        <v>174</v>
+      <c r="B52" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>182</v>
@@ -4361,16 +4460,16 @@
         <v>38</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>183</v>
       </c>
       <c r="G52" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H52" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" s="14" t="s">
         <v>27</v>
@@ -4389,11 +4488,11 @@
       <c r="U52" s="15"/>
     </row>
     <row r="53" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
+      <c r="A53" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="B53" s="25" t="s">
-        <v>174</v>
+      <c r="B53" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>185</v>
@@ -4408,10 +4507,10 @@
         <v>186</v>
       </c>
       <c r="G53" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H53" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I53" s="14" t="s">
         <v>27</v>
@@ -4430,11 +4529,11 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
+      <c r="A54" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B54" s="25" t="s">
-        <v>174</v>
+      <c r="B54" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>188</v>
@@ -4446,16 +4545,16 @@
         <v>25</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G54" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H54" s="14">
-        <v>7</v>
-      </c>
-      <c r="I54" s="14" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="I54" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
@@ -4471,32 +4570,32 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>174</v>
+      <c r="A55" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G55" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H55" s="14">
-        <v>9</v>
-      </c>
-      <c r="I55" s="14" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
@@ -4512,29 +4611,29 @@
       <c r="U55" s="15"/>
     </row>
     <row r="56" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>192</v>
+      <c r="A56" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>194</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G56" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H56" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I56" s="14" t="s">
         <v>27</v>
@@ -4553,29 +4652,29 @@
       <c r="U56" s="15"/>
     </row>
     <row r="57" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B57" s="25" t="s">
-        <v>174</v>
+      <c r="A57" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G57" s="14">
+        <v>2</v>
+      </c>
+      <c r="H57" s="14">
         <v>3</v>
-      </c>
-      <c r="H57" s="14">
-        <v>12</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>27</v>
@@ -4594,29 +4693,29 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>198</v>
+      <c r="A58" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>201</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G58" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I58" s="14" t="s">
         <v>27</v>
@@ -4635,29 +4734,29 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>197</v>
+      <c r="A59" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>202</v>
+        <v>25</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G59" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59" s="14" t="s">
         <v>27</v>
@@ -4676,29 +4775,29 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="B60" s="27" t="s">
-        <v>197</v>
-      </c>
       <c r="C60" s="13" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G60" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H60" s="14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I60" s="14" t="s">
         <v>27</v>
@@ -4717,29 +4816,29 @@
       <c r="U60" s="15"/>
     </row>
     <row r="61" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>197</v>
+      <c r="A61" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G61" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" s="14" t="s">
         <v>27</v>
@@ -4758,29 +4857,29 @@
       <c r="U61" s="15"/>
     </row>
     <row r="62" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>197</v>
+      <c r="A62" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G62" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H62" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I62" s="14" t="s">
         <v>27</v>
@@ -4799,29 +4898,29 @@
       <c r="U62" s="15"/>
     </row>
     <row r="63" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>197</v>
+      <c r="A63" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G63" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H63" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I63" s="14" t="s">
         <v>27</v>
@@ -4840,29 +4939,29 @@
       <c r="U63" s="15"/>
     </row>
     <row r="64" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>197</v>
+      <c r="A64" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G64" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H64" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I64" s="14" t="s">
         <v>27</v>
@@ -4881,29 +4980,29 @@
       <c r="U64" s="15"/>
     </row>
     <row r="65" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>197</v>
+      <c r="A65" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G65" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H65" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I65" s="14" t="s">
         <v>27</v>
@@ -4921,28 +5020,438 @@
       <c r="T65" s="15"/>
       <c r="U65" s="15"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+    <row r="66" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66" s="24" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="28" t="s">
+      <c r="B66" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="28" t="s">
+      <c r="D66" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="13" t="s">
         <v>225</v>
       </c>
+      <c r="G66" s="14">
+        <v>3</v>
+      </c>
+      <c r="H66" s="14">
+        <v>12</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="R66" s="15"/>
+      <c r="S66" s="15"/>
+      <c r="T66" s="15"/>
+      <c r="U66" s="15"/>
+    </row>
+    <row r="67" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="G67" s="14">
+        <v>1</v>
+      </c>
+      <c r="H67" s="14">
+        <v>1</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="R67" s="15"/>
+      <c r="S67" s="15"/>
+      <c r="T67" s="15"/>
+      <c r="U67" s="15"/>
+    </row>
+    <row r="68" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="G68" s="14">
+        <v>4</v>
+      </c>
+      <c r="H68" s="14">
+        <v>4</v>
+      </c>
+      <c r="I68" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="15"/>
+      <c r="S68" s="15"/>
+      <c r="T68" s="15"/>
+      <c r="U68" s="15"/>
+    </row>
+    <row r="69" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="G69" s="14">
+        <v>4</v>
+      </c>
+      <c r="H69" s="14">
+        <v>12</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="R69" s="15"/>
+      <c r="S69" s="15"/>
+      <c r="T69" s="15"/>
+      <c r="U69" s="15"/>
+    </row>
+    <row r="70" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="G70" s="14">
+        <v>1</v>
+      </c>
+      <c r="H70" s="14">
+        <v>4</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="15"/>
+      <c r="T70" s="15"/>
+      <c r="U70" s="15"/>
+    </row>
+    <row r="71" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A71" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G71" s="14">
+        <v>1</v>
+      </c>
+      <c r="H71" s="14">
+        <v>2</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
+      <c r="N71" s="15"/>
+      <c r="O71" s="15"/>
+      <c r="P71" s="15"/>
+      <c r="Q71" s="15"/>
+      <c r="R71" s="15"/>
+      <c r="S71" s="15"/>
+      <c r="T71" s="15"/>
+      <c r="U71" s="15"/>
+    </row>
+    <row r="72" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A72" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="G72" s="14">
+        <v>1</v>
+      </c>
+      <c r="H72" s="14">
+        <v>4</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="15"/>
+      <c r="P72" s="15"/>
+      <c r="Q72" s="15"/>
+      <c r="R72" s="15"/>
+      <c r="S72" s="15"/>
+      <c r="T72" s="15"/>
+      <c r="U72" s="15"/>
+    </row>
+    <row r="73" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G73" s="14">
+        <v>5</v>
+      </c>
+      <c r="H73" s="14">
+        <v>8</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="15"/>
+      <c r="P73" s="15"/>
+      <c r="Q73" s="15"/>
+      <c r="R73" s="15"/>
+      <c r="S73" s="15"/>
+      <c r="T73" s="15"/>
+      <c r="U73" s="15"/>
+    </row>
+    <row r="74" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G74" s="14">
+        <v>3</v>
+      </c>
+      <c r="H74" s="14">
+        <v>4</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="15"/>
+      <c r="P74" s="15"/>
+      <c r="Q74" s="15"/>
+      <c r="R74" s="15"/>
+      <c r="S74" s="15"/>
+      <c r="T74" s="15"/>
+      <c r="U74" s="15"/>
+    </row>
+    <row r="75" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G75" s="14">
+        <v>1</v>
+      </c>
+      <c r="H75" s="14">
+        <v>1</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
+      <c r="R75" s="15"/>
+      <c r="S75" s="15"/>
+      <c r="T75" s="15"/>
+      <c r="U75" s="15"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="28" t="s">
+        <v>258</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I65"/>
+  <autoFilter ref="A5:I75"/>
   <mergeCells count="6">
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
@@ -4951,7 +5460,7 @@
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="T2:U2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:U65">
+  <conditionalFormatting sqref="J6:U75">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($B6="① 土台・ブロッカー",$G6&lt;=J$4,$H6&gt;=J$4)</formula>
     </cfRule>
@@ -4972,10 +5481,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="I10:I65">
+    <dataValidation type="list" allowBlank="1" sqref="I10:I75">
       <formula1>"未着手,進行中,完了,保留,中止"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I6:I65">
+    <dataValidation type="list" allowBlank="1" sqref="I6:I75">
       <formula1>"未着手,進行中,完了,保留,中止"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4996,41 +5505,41 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5038,7 +5547,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="C5" s="31">
         <v>200</v>
@@ -5067,7 +5576,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="C6" s="31">
         <v>350</v>
@@ -5096,7 +5605,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C7" s="31">
         <v>350</v>
@@ -5125,7 +5634,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="C8" s="31">
         <v>250</v>
@@ -5154,7 +5663,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="C9" s="31">
         <v>150</v>
@@ -5183,7 +5692,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="C10" s="31">
         <v>100</v>
@@ -5209,7 +5718,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5222,13 +5731,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="D14" s="39"/>
       <c r="E14" s="39"/>
@@ -5239,13 +5748,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
@@ -5256,13 +5765,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
@@ -5273,13 +5782,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
@@ -5290,13 +5799,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -5307,7 +5816,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -5320,11 +5829,11 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -5335,11 +5844,11 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="41" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
@@ -5350,7 +5859,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -5393,17 +5902,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5425,10 +5934,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
@@ -5441,7 +5950,7 @@
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
       <c r="N5" s="44" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -5449,10 +5958,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="D6" s="43"/>
       <c r="E6" s="43"/>
@@ -5465,7 +5974,7 @@
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
       <c r="N6" s="44" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -5473,10 +5982,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
@@ -5489,7 +5998,7 @@
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
       <c r="N7" s="44" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -5497,10 +6006,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="D8" s="43"/>
       <c r="E8" s="43"/>
@@ -5513,7 +6022,7 @@
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
       <c r="N8" s="44" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -5521,10 +6030,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
@@ -5537,7 +6046,7 @@
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
       <c r="N9" s="45" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -5545,10 +6054,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="D10" s="43"/>
       <c r="E10" s="43"/>
@@ -5561,7 +6070,7 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" s="45" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -5569,10 +6078,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
@@ -5585,7 +6094,7 @@
       <c r="L11" s="43"/>
       <c r="M11" s="43"/>
       <c r="N11" s="45" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -5593,10 +6102,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="D12" s="43"/>
       <c r="E12" s="43"/>
@@ -5609,7 +6118,7 @@
       <c r="L12" s="43"/>
       <c r="M12" s="43"/>
       <c r="N12" s="45" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -5617,10 +6126,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
@@ -5633,12 +6142,12 @@
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
       <c r="N13" s="47" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5657,49 +6166,49 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>295</v>
+        <v>328</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -6464,12 +6973,12 @@
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>307</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6519,17 +7028,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6541,14 +7050,14 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="47">
         <v>30</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
@@ -6557,14 +7066,14 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="47">
         <v>25</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="43"/>
@@ -6573,14 +7082,14 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="47">
         <v>25</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>316</v>
+        <v>349</v>
       </c>
       <c r="E7" s="43"/>
       <c r="F7" s="43"/>
@@ -6589,14 +7098,14 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
-        <v>317</v>
+        <v>350</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="47">
         <v>20</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>318</v>
+        <v>351</v>
       </c>
       <c r="E8" s="43"/>
       <c r="F8" s="43"/>
@@ -6605,7 +7114,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -6617,7 +7126,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="B11" s="50"/>
       <c r="C11" s="50"/>
@@ -6629,7 +7138,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -6641,22 +7150,22 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="B15" s="52" t="s">
         <v>2</v>
@@ -6665,15 +7174,15 @@
         <v>200</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="F15" s="52">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="B16" s="52" t="s">
         <v>3</v>
@@ -6682,15 +7191,15 @@
         <v>350</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="F16" s="52">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="52" t="s">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="B17" s="52" t="s">
         <v>4</v>
@@ -6699,15 +7208,15 @@
         <v>350</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="F17" s="52">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="B18" s="52" t="s">
         <v>5</v>
@@ -6716,15 +7225,15 @@
         <v>250</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="F18" s="52">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="52" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="B19" s="52" t="s">
         <v>6</v>
@@ -6733,7 +7242,7 @@
         <v>150</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="F19" s="52">
         <v>14</v>
@@ -6741,7 +7250,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="B20" s="52" t="s">
         <v>7</v>
@@ -6750,21 +7259,21 @@
         <v>100</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="F20" s="52">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="C21" s="47">
         <v>1400</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="F21" s="52">
         <v>11</v>
@@ -6772,15 +7281,15 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="49" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="F22" s="52">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="49" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="F23" s="52">
         <v>10</v>
@@ -6788,7 +7297,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="49" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="F24" s="52">
         <v>10</v>
@@ -6796,7 +7305,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="49" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="F25" s="52">
         <v>10</v>
@@ -6804,15 +7313,15 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="49" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="F26" s="52">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="49" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="F27" s="52">
         <v>5</v>
@@ -6820,7 +7329,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -6832,28 +7341,28 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -6861,22 +7370,22 @@
         <v>1</v>
       </c>
       <c r="B32" s="55" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="E32" s="54">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G32" s="54">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H32" s="54">
         <v>1</v>
@@ -6887,22 +7396,22 @@
         <v>2</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="E33" s="54">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G33" s="54">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H33" s="54">
         <v>1</v>
@@ -6913,19 +7422,19 @@
         <v>3</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="C34" s="54" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="E34" s="54">
         <v>200</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G34" s="54">
         <v>77</v>
@@ -6939,19 +7448,19 @@
         <v>4</v>
       </c>
       <c r="B35" s="55" t="s">
+        <v>393</v>
+      </c>
+      <c r="C35" s="54" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="54" t="s">
-        <v>327</v>
-      </c>
       <c r="D35" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E35" s="54">
-        <v>150</v>
+        <v>2716</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G35" s="54">
         <v>95</v>
@@ -6965,22 +7474,22 @@
         <v>5</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E36" s="54">
-        <v>2716</v>
+        <v>150</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G36" s="54">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H36" s="54">
         <v>1</v>
@@ -6991,19 +7500,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="C37" s="54" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E37" s="54">
         <v>190</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G37" s="54">
         <v>80</v>
@@ -7017,22 +7526,22 @@
         <v>7</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E38" s="54">
         <v>150</v>
       </c>
       <c r="F38" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G38" s="54">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" s="54">
         <v>1</v>
@@ -7043,22 +7552,22 @@
         <v>8</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E39" s="54">
-        <v>22</v>
+        <v>2170</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G39" s="54">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H39" s="54">
         <v>1</v>
@@ -7069,22 +7578,22 @@
         <v>9</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E40" s="54">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G40" s="54">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="H40" s="54">
         <v>1</v>
@@ -7095,22 +7604,22 @@
         <v>10</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E41" s="54">
-        <v>2170</v>
+        <v>140</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G41" s="54">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H41" s="54">
         <v>1</v>
@@ -7121,19 +7630,19 @@
         <v>11</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E42" s="54">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F42" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G42" s="54">
         <v>73</v>
@@ -7147,22 +7656,22 @@
         <v>12</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E43" s="54">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G43" s="54">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H43" s="54">
         <v>1</v>
@@ -7173,22 +7682,22 @@
         <v>13</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="C44" s="54" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E44" s="54">
         <v>39</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G44" s="54">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H44" s="54">
         <v>1</v>
@@ -7199,22 +7708,22 @@
         <v>14</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="D45" s="55" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="E45" s="54">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G45" s="54">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H45" s="54">
         <v>1</v>
@@ -7225,22 +7734,22 @@
         <v>15</v>
       </c>
       <c r="B46" s="55" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="C46" s="54" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="D46" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E46" s="54">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G46" s="54">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H46" s="54">
         <v>1</v>
@@ -7251,19 +7760,19 @@
         <v>16</v>
       </c>
       <c r="B47" s="55" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="D47" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E47" s="54">
         <v>80</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G47" s="54">
         <v>72</v>
@@ -7277,19 +7786,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="55" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="C48" s="54" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E48" s="54">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="F48" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G48" s="54">
         <v>95</v>
@@ -7303,22 +7812,22 @@
         <v>18</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D49" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E49" s="54">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G49" s="54">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H49" s="54">
         <v>1</v>
@@ -7329,19 +7838,19 @@
         <v>19</v>
       </c>
       <c r="B50" s="55" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C50" s="54" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="D50" s="55" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="E50" s="54" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="F50" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G50" s="54">
         <v>77</v>
@@ -7355,22 +7864,22 @@
         <v>20</v>
       </c>
       <c r="B51" s="55" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="D51" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E51" s="54">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G51" s="54">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="H51" s="54">
         <v>1</v>
@@ -7381,22 +7890,22 @@
         <v>21</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="E52" s="54">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G52" s="54">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H52" s="54">
         <v>1</v>
@@ -7407,22 +7916,22 @@
         <v>22</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>378</v>
+        <v>413</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E53" s="54">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G53" s="54">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H53" s="54">
         <v>1</v>
@@ -7433,22 +7942,22 @@
         <v>23</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E54" s="54">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G54" s="54">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="H54" s="54">
         <v>1</v>
@@ -7459,22 +7968,22 @@
         <v>24</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E55" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E55" s="54">
+        <v>158</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G55" s="54">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H55" s="54">
         <v>1</v>
@@ -7485,22 +7994,22 @@
         <v>25</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="D56" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E56" s="54">
-        <v>40</v>
+        <v>387</v>
+      </c>
+      <c r="E56" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F56" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G56" s="54">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H56" s="54">
         <v>1</v>
@@ -7511,19 +8020,19 @@
         <v>26</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E57" s="54">
         <v>96</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G57" s="54">
         <v>90</v>
@@ -7537,22 +8046,22 @@
         <v>27</v>
       </c>
       <c r="B58" s="55" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="C58" s="54" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="E58" s="54">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G58" s="54">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H58" s="54">
         <v>1</v>
@@ -7563,19 +8072,19 @@
         <v>28</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E59" s="54">
         <v>41</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G59" s="54">
         <v>68</v>
@@ -7589,22 +8098,22 @@
         <v>29</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="C60" s="54" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="D60" s="55" t="s">
         <v>387</v>
       </c>
-      <c r="E60" s="54">
-        <v>120</v>
+      <c r="E60" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F60" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G60" s="54">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H60" s="54">
         <v>1</v>
@@ -7615,22 +8124,22 @@
         <v>30</v>
       </c>
       <c r="B61" s="55" t="s">
+        <v>421</v>
+      </c>
+      <c r="C61" s="54" t="s">
+        <v>377</v>
+      </c>
+      <c r="D61" s="55" t="s">
+        <v>387</v>
+      </c>
+      <c r="E61" s="54">
+        <v>40</v>
+      </c>
+      <c r="F61" s="54" t="s">
         <v>388</v>
       </c>
-      <c r="C61" s="54" t="s">
-        <v>327</v>
-      </c>
-      <c r="D61" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E61" s="54">
-        <v>89</v>
-      </c>
-      <c r="F61" s="54" t="s">
-        <v>355</v>
-      </c>
       <c r="G61" s="54">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="H61" s="54">
         <v>1</v>
@@ -7641,22 +8150,22 @@
         <v>31</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="C62" s="54" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="D62" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E62" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E62" s="54">
+        <v>67</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G62" s="54">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H62" s="54">
         <v>1</v>
@@ -7667,19 +8176,19 @@
         <v>32</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="C63" s="54" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="E63" s="54">
         <v>60</v>
       </c>
       <c r="F63" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G63" s="54">
         <v>67</v>
@@ -7693,22 +8202,22 @@
         <v>33</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="C64" s="54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="E64" s="54">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G64" s="54">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H64" s="54">
         <v>1</v>
@@ -7719,22 +8228,22 @@
         <v>34</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="C65" s="54" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="E65" s="54">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G65" s="54">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H65" s="54">
         <v>1</v>
@@ -7745,22 +8254,22 @@
         <v>35</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="D66" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E66" s="54">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F66" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G66" s="54">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H66" s="54">
         <v>1</v>
@@ -7771,22 +8280,22 @@
         <v>36</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="C67" s="54" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E67" s="54">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G67" s="54">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H67" s="54">
         <v>1</v>
@@ -7797,22 +8306,22 @@
         <v>37</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="C68" s="54" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E68" s="54">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G68" s="54">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H68" s="54">
         <v>1</v>
@@ -7823,22 +8332,22 @@
         <v>38</v>
       </c>
       <c r="B69" s="55" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="C69" s="54" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="D69" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E69" s="54">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>355</v>
+        <v>430</v>
       </c>
       <c r="G69" s="54">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H69" s="54">
         <v>1</v>
@@ -7849,22 +8358,22 @@
         <v>39</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="C70" s="54" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D70" s="55" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="E70" s="54">
-        <v>89</v>
+        <v>1000</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G70" s="54">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H70" s="54">
         <v>1</v>
@@ -7875,22 +8384,22 @@
         <v>40</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="D71" s="55" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E71" s="54">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G71" s="54">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="H71" s="54">
         <v>1</v>
@@ -7901,22 +8410,22 @@
         <v>41</v>
       </c>
       <c r="B72" s="55" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="C72" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D72" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E72" s="54">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="F72" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G72" s="54">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H72" s="54">
         <v>1</v>
@@ -7927,22 +8436,22 @@
         <v>42</v>
       </c>
       <c r="B73" s="55" t="s">
-        <v>401</v>
+        <v>434</v>
       </c>
       <c r="C73" s="54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D73" s="55" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E73" s="54">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G73" s="54">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H73" s="54">
         <v>1</v>
@@ -7953,22 +8462,22 @@
         <v>43</v>
       </c>
       <c r="B74" s="55" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="C74" s="54" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D74" s="55" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="E74" s="54">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G74" s="54">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H74" s="54">
         <v>1</v>
@@ -7979,22 +8488,22 @@
         <v>44</v>
       </c>
       <c r="B75" s="55" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="C75" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D75" s="55" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="E75" s="54">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G75" s="54">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H75" s="54">
         <v>1</v>
@@ -8005,19 +8514,19 @@
         <v>45</v>
       </c>
       <c r="B76" s="55" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="C76" s="54" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="D76" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E76" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E76" s="54">
+        <v>49</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G76" s="54">
         <v>68</v>
@@ -8031,22 +8540,22 @@
         <v>46</v>
       </c>
       <c r="B77" s="55" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="C77" s="54" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D77" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E77" s="54">
-        <v>80</v>
+        <v>387</v>
+      </c>
+      <c r="E77" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F77" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G77" s="54">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="H77" s="54">
         <v>1</v>
@@ -8057,22 +8566,22 @@
         <v>47</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="C78" s="54" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="E78" s="54">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G78" s="54">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H78" s="54">
         <v>1</v>
@@ -8083,22 +8592,22 @@
         <v>48</v>
       </c>
       <c r="B79" s="55" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="C79" s="54" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="D79" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E79" s="54">
-        <v>11</v>
+        <v>390</v>
+      </c>
+      <c r="E79" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G79" s="54">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H79" s="54">
         <v>1</v>
@@ -8109,22 +8618,22 @@
         <v>49</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="C80" s="54" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>359</v>
+        <v>435</v>
       </c>
       <c r="E80" s="54">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="G80" s="54">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H80" s="54">
         <v>1</v>
@@ -8135,22 +8644,22 @@
         <v>50</v>
       </c>
       <c r="B81" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="C81" s="54" t="s">
+        <v>368</v>
+      </c>
+      <c r="D81" s="55" t="s">
+        <v>387</v>
+      </c>
+      <c r="E81" s="54" t="s">
         <v>410</v>
       </c>
-      <c r="C81" s="54" t="s">
-        <v>340</v>
-      </c>
-      <c r="D81" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E81" s="54" t="s">
-        <v>377</v>
-      </c>
       <c r="F81" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G81" s="54">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H81" s="54">
         <v>1</v>
@@ -8161,22 +8670,22 @@
         <v>51</v>
       </c>
       <c r="B82" s="55" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="C82" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="E82" s="54">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F82" s="54" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="G82" s="54">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H82" s="54">
         <v>1</v>
@@ -8187,22 +8696,22 @@
         <v>52</v>
       </c>
       <c r="B83" s="55" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="C83" s="54" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="D83" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E83" s="54">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G83" s="54">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H83" s="54">
         <v>1</v>
@@ -8213,22 +8722,22 @@
         <v>53</v>
       </c>
       <c r="B84" s="55" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="C84" s="54" t="s">
-        <v>335</v>
+        <v>375</v>
       </c>
       <c r="D84" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E84" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E84" s="54">
+        <v>36</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G84" s="54">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H84" s="54">
         <v>1</v>
@@ -8239,22 +8748,22 @@
         <v>54</v>
       </c>
       <c r="B85" s="55" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="C85" s="54" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D85" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E85" s="54">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G85" s="54">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H85" s="54">
         <v>1</v>
@@ -8265,22 +8774,22 @@
         <v>55</v>
       </c>
       <c r="B86" s="55" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="C86" s="54" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="D86" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E86" s="54">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F86" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G86" s="54">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H86" s="54">
         <v>1</v>
@@ -8291,19 +8800,19 @@
         <v>56</v>
       </c>
       <c r="B87" s="55" t="s">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="C87" s="54" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="D87" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E87" s="54">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G87" s="54">
         <v>72</v>
@@ -8317,22 +8826,22 @@
         <v>57</v>
       </c>
       <c r="B88" s="55" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="C88" s="54" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="D88" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E88" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E88" s="54">
+        <v>70</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G88" s="54">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H88" s="54">
         <v>1</v>
@@ -8343,22 +8852,22 @@
         <v>58</v>
       </c>
       <c r="B89" s="55" t="s">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="C89" s="54" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="D89" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E89" s="54">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G89" s="54">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="H89" s="54">
         <v>1</v>
@@ -8369,22 +8878,22 @@
         <v>59</v>
       </c>
       <c r="B90" s="55" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="C90" s="54" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="D90" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E90" s="54">
-        <v>110</v>
+        <v>390</v>
+      </c>
+      <c r="E90" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F90" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G90" s="54">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H90" s="54">
         <v>1</v>
@@ -8395,22 +8904,22 @@
         <v>60</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="C91" s="54" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="D91" s="55" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="E91" s="54">
         <v>70</v>
       </c>
       <c r="F91" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G91" s="54">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H91" s="54">
         <v>1</v>
@@ -8421,22 +8930,22 @@
         <v>61</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="C92" s="54" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D92" s="55" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="E92" s="54">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F92" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G92" s="54">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H92" s="54">
         <v>1</v>
@@ -8447,22 +8956,22 @@
         <v>62</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="C93" s="54" t="s">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="D93" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E93" s="54">
-        <v>62</v>
+        <v>387</v>
+      </c>
+      <c r="E93" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F93" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G93" s="54">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="H93" s="54">
         <v>1</v>
@@ -8473,22 +8982,22 @@
         <v>63</v>
       </c>
       <c r="B94" s="55" t="s">
-        <v>423</v>
+        <v>456</v>
       </c>
       <c r="C94" s="54" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E94" s="54">
-        <v>107</v>
+        <v>387</v>
+      </c>
+      <c r="E94" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F94" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G94" s="54">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H94" s="54">
         <v>1</v>
@@ -8499,22 +9008,22 @@
         <v>64</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>424</v>
+        <v>457</v>
       </c>
       <c r="C95" s="54" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="D95" s="55" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="E95" s="54" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="F95" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G95" s="54">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H95" s="54">
         <v>1</v>
@@ -8525,22 +9034,22 @@
         <v>65</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="C96" s="54" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E96" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E96" s="54">
+        <v>100</v>
       </c>
       <c r="F96" s="54" t="s">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="G96" s="54">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="H96" s="54">
         <v>1</v>
@@ -8551,22 +9060,22 @@
         <v>66</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="C97" s="54" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="E97" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E97" s="54">
+        <v>60</v>
       </c>
       <c r="F97" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G97" s="54">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H97" s="54">
         <v>1</v>
@@ -8577,22 +9086,22 @@
         <v>67</v>
       </c>
       <c r="B98" s="55" t="s">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="C98" s="54" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="E98" s="54" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="F98" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G98" s="54">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H98" s="54">
         <v>1</v>
@@ -8603,22 +9112,22 @@
         <v>68</v>
       </c>
       <c r="B99" s="55" t="s">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="C99" s="54" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E99" s="54">
-        <v>60</v>
+        <v>390</v>
+      </c>
+      <c r="E99" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F99" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G99" s="54">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H99" s="54">
         <v>1</v>
@@ -8629,22 +9138,22 @@
         <v>69</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="C100" s="54" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E100" s="54">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F100" s="54" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="G100" s="54">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="H100" s="54">
         <v>1</v>
@@ -8655,22 +9164,22 @@
         <v>70</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="C101" s="54" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E101" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E101" s="54">
+        <v>67</v>
       </c>
       <c r="F101" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G101" s="54">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H101" s="54">
         <v>1</v>
@@ -8681,22 +9190,22 @@
         <v>71</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="C102" s="54" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="E102" s="54">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F102" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G102" s="54">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H102" s="54">
         <v>1</v>
@@ -8707,22 +9216,22 @@
         <v>72</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="C103" s="54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D103" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E103" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E103" s="54">
+        <v>100</v>
       </c>
       <c r="F103" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G103" s="54">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H103" s="54">
         <v>1</v>
@@ -8733,22 +9242,22 @@
         <v>73</v>
       </c>
       <c r="B104" s="55" t="s">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="C104" s="54" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D104" s="55" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="E104" s="54">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F104" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G104" s="54">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H104" s="54">
         <v>1</v>
@@ -8759,22 +9268,22 @@
         <v>74</v>
       </c>
       <c r="B105" s="55" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="C105" s="54" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="D105" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E105" s="54">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F105" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G105" s="54">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H105" s="54">
         <v>1</v>
@@ -8785,22 +9294,22 @@
         <v>75</v>
       </c>
       <c r="B106" s="55" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C106" s="54" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="D106" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E106" s="54">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F106" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G106" s="54">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H106" s="54">
         <v>1</v>
@@ -8811,22 +9320,22 @@
         <v>76</v>
       </c>
       <c r="B107" s="55" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="C107" s="54" t="s">
-        <v>327</v>
+        <v>376</v>
       </c>
       <c r="D107" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E107" s="54">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F107" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G107" s="54">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H107" s="54">
         <v>1</v>
@@ -8837,22 +9346,22 @@
         <v>77</v>
       </c>
       <c r="B108" s="55" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="C108" s="54" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D108" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E108" s="54">
         <v>100</v>
       </c>
       <c r="F108" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G108" s="54">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H108" s="54">
         <v>1</v>
@@ -8863,22 +9372,22 @@
         <v>78</v>
       </c>
       <c r="B109" s="55" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="C109" s="54" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="D109" s="55" t="s">
-        <v>371</v>
-      </c>
-      <c r="E109" s="54">
-        <v>40</v>
+        <v>390</v>
+      </c>
+      <c r="E109" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F109" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G109" s="54">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H109" s="54">
         <v>1</v>
@@ -8889,22 +9398,22 @@
         <v>79</v>
       </c>
       <c r="B110" s="55" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="C110" s="54" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D110" s="55" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="E110" s="54">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F110" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G110" s="54">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H110" s="54">
         <v>1</v>
@@ -8915,22 +9424,22 @@
         <v>80</v>
       </c>
       <c r="B111" s="55" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="C111" s="54" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="D111" s="55" t="s">
-        <v>404</v>
-      </c>
-      <c r="E111" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E111" s="54">
+        <v>54</v>
       </c>
       <c r="F111" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G111" s="54">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H111" s="54">
         <v>1</v>
@@ -8941,22 +9450,22 @@
         <v>81</v>
       </c>
       <c r="B112" s="55" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="C112" s="54" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="D112" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E112" s="54">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="F112" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G112" s="54">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="H112" s="54">
         <v>1</v>
@@ -8967,22 +9476,22 @@
         <v>82</v>
       </c>
       <c r="B113" s="55" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="C113" s="54" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="D113" s="55" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E113" s="54">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="F113" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G113" s="54">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H113" s="54">
         <v>1</v>
@@ -8993,22 +9502,22 @@
         <v>83</v>
       </c>
       <c r="B114" s="55" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="C114" s="54" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="D114" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E114" s="54">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="F114" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G114" s="54">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H114" s="54">
         <v>1</v>
@@ -9019,22 +9528,22 @@
         <v>84</v>
       </c>
       <c r="B115" s="55" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="C115" s="54" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="D115" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E115" s="54">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F115" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G115" s="54">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="H115" s="54">
         <v>1</v>
@@ -9045,22 +9554,22 @@
         <v>85</v>
       </c>
       <c r="B116" s="55" t="s">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="C116" s="54" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D116" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E116" s="54">
-        <v>50</v>
+        <v>435</v>
+      </c>
+      <c r="E116" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F116" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G116" s="54">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H116" s="54">
         <v>1</v>
@@ -9071,22 +9580,22 @@
         <v>86</v>
       </c>
       <c r="B117" s="55" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="C117" s="54" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="D117" s="55" t="s">
-        <v>371</v>
-      </c>
-      <c r="E117" s="54">
-        <v>300</v>
+        <v>390</v>
+      </c>
+      <c r="E117" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F117" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G117" s="54">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="H117" s="54">
         <v>1</v>
@@ -9097,22 +9606,22 @@
         <v>87</v>
       </c>
       <c r="B118" s="55" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="C118" s="54" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="D118" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E118" s="54" t="s">
-        <v>377</v>
+        <v>405</v>
+      </c>
+      <c r="E118" s="54">
+        <v>250</v>
       </c>
       <c r="F118" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G118" s="54">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H118" s="54">
         <v>1</v>
@@ -9123,22 +9632,22 @@
         <v>88</v>
       </c>
       <c r="B119" s="55" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="C119" s="54" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D119" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E119" s="54">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F119" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G119" s="54">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H119" s="54">
         <v>1</v>
@@ -9149,22 +9658,22 @@
         <v>89</v>
       </c>
       <c r="B120" s="55" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="C120" s="54" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="D120" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E120" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E120" s="54">
+        <v>67</v>
       </c>
       <c r="F120" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G120" s="54">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H120" s="54">
         <v>1</v>
@@ -9175,22 +9684,22 @@
         <v>90</v>
       </c>
       <c r="B121" s="55" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="C121" s="54" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="D121" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E121" s="54">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F121" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G121" s="54">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H121" s="54">
         <v>1</v>
@@ -9201,19 +9710,19 @@
         <v>91</v>
       </c>
       <c r="B122" s="55" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="C122" s="54" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="D122" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E122" s="54">
         <v>50</v>
       </c>
       <c r="F122" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G122" s="54">
         <v>90</v>
@@ -9227,22 +9736,22 @@
         <v>92</v>
       </c>
       <c r="B123" s="55" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="C123" s="54" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="D123" s="55" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E123" s="54">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F123" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G123" s="54">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H123" s="54">
         <v>1</v>
@@ -9253,22 +9762,22 @@
         <v>93</v>
       </c>
       <c r="B124" s="55" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="C124" s="54" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="D124" s="55" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E124" s="54">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="F124" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G124" s="54">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H124" s="54">
         <v>1</v>
@@ -9279,19 +9788,19 @@
         <v>94</v>
       </c>
       <c r="B125" s="55" t="s">
-        <v>418</v>
+        <v>487</v>
       </c>
       <c r="C125" s="54" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="D125" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E125" s="54">
-        <v>80</v>
+        <v>390</v>
+      </c>
+      <c r="E125" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F125" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G125" s="54">
         <v>72</v>
@@ -9305,22 +9814,22 @@
         <v>95</v>
       </c>
       <c r="B126" s="55" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="C126" s="54" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D126" s="55" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="E126" s="54">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="F126" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G126" s="54">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H126" s="54">
         <v>1</v>
@@ -9331,22 +9840,22 @@
         <v>96</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="C127" s="54" t="s">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="D127" s="55" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="E127" s="54">
-        <v>600</v>
+        <v>5</v>
       </c>
       <c r="F127" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G127" s="54">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="H127" s="54">
         <v>1</v>
@@ -9357,19 +9866,19 @@
         <v>97</v>
       </c>
       <c r="B128" s="55" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C128" s="54" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="D128" s="55" t="s">
-        <v>404</v>
-      </c>
-      <c r="E128" s="54" t="s">
-        <v>377</v>
+        <v>390</v>
+      </c>
+      <c r="E128" s="54">
+        <v>80</v>
       </c>
       <c r="F128" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G128" s="54">
         <v>72</v>
@@ -9383,22 +9892,22 @@
         <v>98</v>
       </c>
       <c r="B129" s="55" t="s">
-        <v>457</v>
+        <v>490</v>
       </c>
       <c r="C129" s="54" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="D129" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E129" s="54">
-        <v>6</v>
+        <v>390</v>
+      </c>
+      <c r="E129" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="F129" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G129" s="54">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H129" s="54">
         <v>1</v>
@@ -9409,22 +9918,22 @@
         <v>99</v>
       </c>
       <c r="B130" s="55" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="C130" s="54" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D130" s="55" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="E130" s="54">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="F130" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G130" s="54">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H130" s="54">
         <v>1</v>
@@ -9435,22 +9944,22 @@
         <v>100</v>
       </c>
       <c r="B131" s="55" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="C131" s="54" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="D131" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="E131" s="54" t="s">
-        <v>377</v>
+        <v>392</v>
+      </c>
+      <c r="E131" s="54">
+        <v>136</v>
       </c>
       <c r="F131" s="54" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="G131" s="54">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="H131" s="54">
         <v>1</v>
@@ -9488,7 +9997,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>460</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -9498,27 +10007,27 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>465</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -9528,17 +10037,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>466</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -9548,37 +10057,37 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>470</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -9588,22 +10097,22 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>478</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -9613,27 +10122,27 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>481</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>482</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>483</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -9643,17 +10152,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>485</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>487</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
+++ b/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="520">
   <si>
     <t>ProofLoop タスクシート 2026-08 → 2027-01（最終更新 2026-08-11）</t>
   </si>
@@ -599,22 +599,19 @@
     <t>D9</t>
   </si>
   <si>
-    <t>★claimオーナーが応募（ATS・応募DM）に到達できない</t>
-  </si>
-  <si>
-    <t>オーナー判断→Claude</t>
-  </si>
-  <si>
-    <t>applications/application_messages のRLSをメンバー起点へ</t>
+    <t>応募RLSのメンバー起点移行（claimオーナーが応募を見られない）</t>
+  </si>
+  <si>
+    <t>035で5本のポリシーを移行。応募0件のいま直す</t>
   </si>
   <si>
     <t>D10</t>
   </si>
   <si>
-    <t>/organizations/[id] の ISR 導入（流入時の負荷対策）</t>
-  </si>
-  <si>
-    <t>1アクセス毎のサーバ処理を減らす。claim_status の鮮度と要トレードオフ</t>
+    <t>/organizations/[id] の ISR ＋ オンデマンド再検証</t>
+  </si>
+  <si>
+    <t>ISRだけだと凍結が最大N秒遅れる。claim変更時に再検証</t>
   </si>
   <si>
     <t>D11</t>
@@ -4617,26 +4614,26 @@
       <c r="B56" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="13" t="s">
         <v>194</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>49</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G56" s="14">
+        <v>1</v>
+      </c>
+      <c r="H56" s="14">
         <v>2</v>
       </c>
-      <c r="H56" s="14">
-        <v>4</v>
-      </c>
       <c r="I56" s="14" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
@@ -4653,31 +4650,31 @@
     </row>
     <row r="57" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>169</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G57" s="14">
+        <v>1</v>
+      </c>
+      <c r="H57" s="14">
         <v>2</v>
       </c>
-      <c r="H57" s="14">
-        <v>3</v>
-      </c>
       <c r="I57" s="14" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
@@ -4694,13 +4691,13 @@
     </row>
     <row r="58" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="23" t="s">
         <v>169</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>38</v>
@@ -4709,7 +4706,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G58" s="14">
         <v>3</v>
@@ -4735,22 +4732,22 @@
     </row>
     <row r="59" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="C59" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="14" t="s">
         <v>205</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>206</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G59" s="14">
         <v>1</v>
@@ -4776,13 +4773,13 @@
     </row>
     <row r="60" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>209</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>38</v>
@@ -4791,7 +4788,7 @@
         <v>25</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G60" s="14">
         <v>2</v>
@@ -4817,13 +4814,13 @@
     </row>
     <row r="61" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>211</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>212</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>38</v>
@@ -4832,7 +4829,7 @@
         <v>168</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G61" s="14">
         <v>3</v>
@@ -4858,13 +4855,13 @@
     </row>
     <row r="62" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>38</v>
@@ -4873,7 +4870,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G62" s="14">
         <v>5</v>
@@ -4899,13 +4896,13 @@
     </row>
     <row r="63" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="B63" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>38</v>
@@ -4914,7 +4911,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G63" s="14">
         <v>7</v>
@@ -4940,13 +4937,13 @@
     </row>
     <row r="64" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="B64" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>38</v>
@@ -4955,7 +4952,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G64" s="14">
         <v>9</v>
@@ -4981,13 +4978,13 @@
     </row>
     <row r="65" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C65" s="13" t="s">
         <v>221</v>
-      </c>
-      <c r="B65" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>222</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>38</v>
@@ -4996,7 +4993,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G65" s="14">
         <v>11</v>
@@ -5022,13 +5019,13 @@
     </row>
     <row r="66" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="B66" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>38</v>
@@ -5037,7 +5034,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G66" s="14">
         <v>3</v>
@@ -5063,13 +5060,13 @@
     </row>
     <row r="67" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="C67" s="21" t="s">
         <v>227</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>228</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>30</v>
@@ -5078,7 +5075,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G67" s="14">
         <v>1</v>
@@ -5104,22 +5101,22 @@
     </row>
     <row r="68" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E68" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>232</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>233</v>
       </c>
       <c r="G68" s="14">
         <v>4</v>
@@ -5145,22 +5142,22 @@
     </row>
     <row r="69" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="B69" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>235</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G69" s="14">
         <v>4</v>
@@ -5186,13 +5183,13 @@
     </row>
     <row r="70" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>238</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>30</v>
@@ -5201,7 +5198,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G70" s="14">
         <v>1</v>
@@ -5227,13 +5224,13 @@
     </row>
     <row r="71" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C71" s="13" t="s">
         <v>240</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>30</v>
@@ -5242,7 +5239,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G71" s="14">
         <v>1</v>
@@ -5268,13 +5265,13 @@
     </row>
     <row r="72" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>244</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>30</v>
@@ -5283,7 +5280,7 @@
         <v>25</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G72" s="14">
         <v>1</v>
@@ -5309,13 +5306,13 @@
     </row>
     <row r="73" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>30</v>
@@ -5324,7 +5321,7 @@
         <v>25</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G73" s="14">
         <v>5</v>
@@ -5350,13 +5347,13 @@
     </row>
     <row r="74" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>249</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>250</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>30</v>
@@ -5365,7 +5362,7 @@
         <v>21</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G74" s="14">
         <v>3</v>
@@ -5391,13 +5388,13 @@
     </row>
     <row r="75" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>252</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>253</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>30</v>
@@ -5406,7 +5403,7 @@
         <v>175</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G75" s="14">
         <v>1</v>
@@ -5432,22 +5429,22 @@
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5505,41 +5502,41 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5547,7 +5544,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C5" s="31">
         <v>200</v>
@@ -5576,7 +5573,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="31">
         <v>350</v>
@@ -5605,7 +5602,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C7" s="31">
         <v>350</v>
@@ -5634,7 +5631,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C8" s="31">
         <v>250</v>
@@ -5663,7 +5660,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C9" s="31">
         <v>150</v>
@@ -5692,7 +5689,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10" s="31">
         <v>100</v>
@@ -5718,7 +5715,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5731,13 +5728,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="C14" s="39" t="s">
         <v>278</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>279</v>
       </c>
       <c r="D14" s="39"/>
       <c r="E14" s="39"/>
@@ -5748,13 +5745,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="C15" s="39" t="s">
         <v>281</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>282</v>
       </c>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
@@ -5765,13 +5762,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="B16" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="C16" s="39" t="s">
         <v>284</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>285</v>
       </c>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
@@ -5782,13 +5779,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="B17" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="C17" s="39" t="s">
         <v>287</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>288</v>
       </c>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
@@ -5799,13 +5796,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="C18" s="39" t="s">
         <v>290</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>291</v>
       </c>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -5816,7 +5813,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -5829,11 +5826,11 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -5844,11 +5841,11 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
@@ -5859,7 +5856,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -5902,17 +5899,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5934,10 +5931,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>301</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>302</v>
       </c>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
@@ -5950,7 +5947,7 @@
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
       <c r="N5" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -5958,10 +5955,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>304</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>305</v>
       </c>
       <c r="D6" s="43"/>
       <c r="E6" s="43"/>
@@ -5974,7 +5971,7 @@
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
       <c r="N6" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -5982,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>306</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>307</v>
       </c>
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
@@ -5998,7 +5995,7 @@
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
       <c r="N7" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6006,10 +6003,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>308</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>309</v>
       </c>
       <c r="D8" s="43"/>
       <c r="E8" s="43"/>
@@ -6022,7 +6019,7 @@
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
       <c r="N8" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -6030,10 +6027,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>310</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>311</v>
       </c>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
@@ -6046,7 +6043,7 @@
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
       <c r="N9" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -6054,10 +6051,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>313</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>314</v>
       </c>
       <c r="D10" s="43"/>
       <c r="E10" s="43"/>
@@ -6070,7 +6067,7 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -6078,10 +6075,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>315</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>316</v>
       </c>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
@@ -6094,7 +6091,7 @@
       <c r="L11" s="43"/>
       <c r="M11" s="43"/>
       <c r="N11" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -6102,10 +6099,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="C12" s="43" t="s">
         <v>317</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>318</v>
       </c>
       <c r="D12" s="43"/>
       <c r="E12" s="43"/>
@@ -6118,7 +6115,7 @@
       <c r="L12" s="43"/>
       <c r="M12" s="43"/>
       <c r="N12" s="45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -6126,10 +6123,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>320</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>321</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
@@ -6142,12 +6139,12 @@
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
       <c r="N13" s="47" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6166,49 +6163,49 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="J16" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="L16" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>337</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -6973,12 +6970,12 @@
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7028,17 +7025,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7050,14 +7047,14 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="47">
         <v>30</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
@@ -7066,14 +7063,14 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="47">
         <v>25</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="43"/>
@@ -7082,14 +7079,14 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="47">
         <v>25</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E7" s="43"/>
       <c r="F7" s="43"/>
@@ -7098,14 +7095,14 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="47">
         <v>20</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E8" s="43"/>
       <c r="F8" s="43"/>
@@ -7114,7 +7111,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -7126,7 +7123,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B11" s="50"/>
       <c r="C11" s="50"/>
@@ -7138,7 +7135,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -7150,22 +7147,22 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="E14" s="51" t="s">
         <v>357</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>358</v>
       </c>
       <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15" s="52" t="s">
         <v>2</v>
@@ -7174,7 +7171,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F15" s="52">
         <v>37</v>
@@ -7182,7 +7179,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B16" s="52" t="s">
         <v>3</v>
@@ -7191,7 +7188,7 @@
         <v>350</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F16" s="52">
         <v>36</v>
@@ -7199,7 +7196,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="52" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B17" s="52" t="s">
         <v>4</v>
@@ -7208,7 +7205,7 @@
         <v>350</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F17" s="52">
         <v>24</v>
@@ -7216,7 +7213,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B18" s="52" t="s">
         <v>5</v>
@@ -7225,7 +7222,7 @@
         <v>250</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F18" s="52">
         <v>15</v>
@@ -7233,7 +7230,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="52" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B19" s="52" t="s">
         <v>6</v>
@@ -7242,7 +7239,7 @@
         <v>150</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F19" s="52">
         <v>14</v>
@@ -7250,7 +7247,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B20" s="52" t="s">
         <v>7</v>
@@ -7259,7 +7256,7 @@
         <v>100</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F20" s="52">
         <v>12</v>
@@ -7267,13 +7264,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C21" s="47">
         <v>1400</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F21" s="52">
         <v>11</v>
@@ -7281,7 +7278,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="49" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F22" s="52">
         <v>11</v>
@@ -7289,7 +7286,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F23" s="52">
         <v>10</v>
@@ -7297,7 +7294,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="49" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F24" s="52">
         <v>10</v>
@@ -7305,7 +7302,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F25" s="52">
         <v>10</v>
@@ -7313,7 +7310,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F26" s="52">
         <v>5</v>
@@ -7321,7 +7318,7 @@
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F27" s="52">
         <v>5</v>
@@ -7329,7 +7326,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -7341,28 +7338,28 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="D31" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="F31" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G31" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>385</v>
-      </c>
       <c r="H31" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -7370,19 +7367,19 @@
         <v>1</v>
       </c>
       <c r="B32" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="D32" s="55" t="s">
         <v>386</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>360</v>
-      </c>
-      <c r="D32" s="55" t="s">
-        <v>387</v>
       </c>
       <c r="E32" s="54">
         <v>257</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G32" s="54">
         <v>100</v>
@@ -7396,19 +7393,19 @@
         <v>2</v>
       </c>
       <c r="B33" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="D33" s="55" t="s">
         <v>389</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>362</v>
-      </c>
-      <c r="D33" s="55" t="s">
-        <v>390</v>
       </c>
       <c r="E33" s="54">
         <v>200</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G33" s="54">
         <v>95</v>
@@ -7422,19 +7419,19 @@
         <v>3</v>
       </c>
       <c r="B34" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="D34" s="55" t="s">
         <v>391</v>
-      </c>
-      <c r="C34" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="D34" s="55" t="s">
-        <v>392</v>
       </c>
       <c r="E34" s="54">
         <v>200</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G34" s="54">
         <v>77</v>
@@ -7448,19 +7445,19 @@
         <v>4</v>
       </c>
       <c r="B35" s="55" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E35" s="54">
         <v>2716</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G35" s="54">
         <v>95</v>
@@ -7474,19 +7471,19 @@
         <v>5</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E36" s="54">
         <v>150</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G36" s="54">
         <v>95</v>
@@ -7500,19 +7497,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C37" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E37" s="54">
         <v>190</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G37" s="54">
         <v>80</v>
@@ -7526,19 +7523,19 @@
         <v>7</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E38" s="54">
         <v>150</v>
       </c>
       <c r="F38" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G38" s="54">
         <v>80</v>
@@ -7552,19 +7549,19 @@
         <v>8</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E39" s="54">
         <v>2170</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G39" s="54">
         <v>95</v>
@@ -7578,19 +7575,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E40" s="54">
         <v>22</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G40" s="54">
         <v>77</v>
@@ -7604,19 +7601,19 @@
         <v>10</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E41" s="54">
         <v>140</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G41" s="54">
         <v>95</v>
@@ -7630,19 +7627,19 @@
         <v>11</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E42" s="54">
         <v>60</v>
       </c>
       <c r="F42" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G42" s="54">
         <v>73</v>
@@ -7656,19 +7653,19 @@
         <v>12</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E43" s="54">
         <v>54</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G43" s="54">
         <v>73</v>
@@ -7682,19 +7679,19 @@
         <v>13</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C44" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E44" s="54">
         <v>39</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G44" s="54">
         <v>68</v>
@@ -7708,19 +7705,19 @@
         <v>14</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D45" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E45" s="54">
         <v>108</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G45" s="54">
         <v>77</v>
@@ -7734,19 +7731,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="55" t="s">
+        <v>403</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>374</v>
+      </c>
+      <c r="D46" s="55" t="s">
         <v>404</v>
-      </c>
-      <c r="C46" s="54" t="s">
-        <v>375</v>
-      </c>
-      <c r="D46" s="55" t="s">
-        <v>405</v>
       </c>
       <c r="E46" s="54">
         <v>60</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G46" s="54">
         <v>67</v>
@@ -7760,19 +7757,19 @@
         <v>16</v>
       </c>
       <c r="B47" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D47" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E47" s="54">
         <v>80</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G47" s="54">
         <v>72</v>
@@ -7786,19 +7783,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C48" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E48" s="54">
         <v>200</v>
       </c>
       <c r="F48" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G48" s="54">
         <v>95</v>
@@ -7812,19 +7809,19 @@
         <v>18</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D49" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E49" s="54">
         <v>125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G49" s="54">
         <v>95</v>
@@ -7838,19 +7835,19 @@
         <v>19</v>
       </c>
       <c r="B50" s="55" t="s">
+        <v>408</v>
+      </c>
+      <c r="C50" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="D50" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E50" s="54" t="s">
         <v>409</v>
       </c>
-      <c r="C50" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="D50" s="55" t="s">
+      <c r="F50" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E50" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F50" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G50" s="54">
         <v>77</v>
@@ -7864,19 +7861,19 @@
         <v>20</v>
       </c>
       <c r="B51" s="55" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D51" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E51" s="54">
         <v>200</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G51" s="54">
         <v>75</v>
@@ -7890,19 +7887,19 @@
         <v>21</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E52" s="54">
         <v>165</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G52" s="54">
         <v>95</v>
@@ -7916,19 +7913,19 @@
         <v>22</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E53" s="54">
         <v>70</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G53" s="54">
         <v>75</v>
@@ -7942,19 +7939,19 @@
         <v>23</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E54" s="54">
         <v>100</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G54" s="54">
         <v>95</v>
@@ -7968,19 +7965,19 @@
         <v>24</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E55" s="54">
         <v>158</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G55" s="54">
         <v>95</v>
@@ -7994,19 +7991,19 @@
         <v>25</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D56" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E56" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F56" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E56" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F56" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G56" s="54">
         <v>77</v>
@@ -8020,19 +8017,19 @@
         <v>26</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E57" s="54">
         <v>96</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G57" s="54">
         <v>90</v>
@@ -8046,19 +8043,19 @@
         <v>27</v>
       </c>
       <c r="B58" s="55" t="s">
+        <v>416</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>369</v>
+      </c>
+      <c r="D58" s="55" t="s">
         <v>417</v>
-      </c>
-      <c r="C58" s="54" t="s">
-        <v>370</v>
-      </c>
-      <c r="D58" s="55" t="s">
-        <v>418</v>
       </c>
       <c r="E58" s="54">
         <v>120</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G58" s="54">
         <v>68</v>
@@ -8072,19 +8069,19 @@
         <v>28</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E59" s="54">
         <v>41</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G59" s="54">
         <v>68</v>
@@ -8098,19 +8095,19 @@
         <v>29</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C60" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D60" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E60" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F60" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E60" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F60" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G60" s="54">
         <v>68</v>
@@ -8124,19 +8121,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C61" s="54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D61" s="55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E61" s="54">
         <v>40</v>
       </c>
       <c r="F61" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G61" s="54">
         <v>69</v>
@@ -8150,19 +8147,19 @@
         <v>31</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C62" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D62" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E62" s="54">
         <v>67</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G62" s="54">
         <v>72</v>
@@ -8176,19 +8173,19 @@
         <v>32</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E63" s="54">
         <v>60</v>
       </c>
       <c r="F63" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G63" s="54">
         <v>67</v>
@@ -8202,19 +8199,19 @@
         <v>33</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C64" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E64" s="54">
         <v>150</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G64" s="54">
         <v>95</v>
@@ -8228,19 +8225,19 @@
         <v>34</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E65" s="54">
         <v>89</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G65" s="54">
         <v>90</v>
@@ -8254,19 +8251,19 @@
         <v>35</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D66" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E66" s="54">
         <v>57</v>
       </c>
       <c r="F66" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G66" s="54">
         <v>63</v>
@@ -8280,19 +8277,19 @@
         <v>36</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C67" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E67" s="54">
         <v>54</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G67" s="54">
         <v>75</v>
@@ -8306,19 +8303,19 @@
         <v>37</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C68" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E68" s="54">
         <v>80</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G68" s="54">
         <v>72</v>
@@ -8332,19 +8329,19 @@
         <v>38</v>
       </c>
       <c r="B69" s="55" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C69" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D69" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E69" s="54">
         <v>200</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G69" s="54">
         <v>72</v>
@@ -8358,19 +8355,19 @@
         <v>39</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C70" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D70" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E70" s="54">
         <v>1000</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G70" s="54">
         <v>70</v>
@@ -8384,19 +8381,19 @@
         <v>40</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D71" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E71" s="54">
         <v>120</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G71" s="54">
         <v>95</v>
@@ -8410,19 +8407,19 @@
         <v>41</v>
       </c>
       <c r="B72" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C72" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D72" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E72" s="54">
         <v>83</v>
       </c>
       <c r="F72" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G72" s="54">
         <v>90</v>
@@ -8436,19 +8433,19 @@
         <v>42</v>
       </c>
       <c r="B73" s="55" t="s">
+        <v>433</v>
+      </c>
+      <c r="C73" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="D73" s="55" t="s">
         <v>434</v>
-      </c>
-      <c r="C73" s="54" t="s">
-        <v>360</v>
-      </c>
-      <c r="D73" s="55" t="s">
-        <v>435</v>
       </c>
       <c r="E73" s="54">
         <v>120</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G73" s="54">
         <v>95</v>
@@ -8462,19 +8459,19 @@
         <v>43</v>
       </c>
       <c r="B74" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C74" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D74" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E74" s="54">
         <v>50</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G74" s="54">
         <v>72</v>
@@ -8488,19 +8485,19 @@
         <v>44</v>
       </c>
       <c r="B75" s="55" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C75" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D75" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E75" s="54">
         <v>80</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G75" s="54">
         <v>90</v>
@@ -8514,19 +8511,19 @@
         <v>45</v>
       </c>
       <c r="B76" s="55" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C76" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D76" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E76" s="54">
         <v>49</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G76" s="54">
         <v>68</v>
@@ -8540,19 +8537,19 @@
         <v>46</v>
       </c>
       <c r="B77" s="55" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C77" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D77" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E77" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F77" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E77" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F77" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G77" s="54">
         <v>68</v>
@@ -8566,19 +8563,19 @@
         <v>47</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C78" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E78" s="54">
         <v>200</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G78" s="54">
         <v>70</v>
@@ -8592,19 +8589,19 @@
         <v>48</v>
       </c>
       <c r="B79" s="55" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C79" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D79" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E79" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G79" s="54">
         <v>63</v>
@@ -8618,19 +8615,19 @@
         <v>49</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C80" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E80" s="54">
         <v>120</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G80" s="54">
         <v>95</v>
@@ -8644,19 +8641,19 @@
         <v>50</v>
       </c>
       <c r="B81" s="55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C81" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D81" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E81" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F81" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E81" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F81" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G81" s="54">
         <v>70</v>
@@ -8670,19 +8667,19 @@
         <v>51</v>
       </c>
       <c r="B82" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C82" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E82" s="54">
         <v>80</v>
       </c>
       <c r="F82" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G82" s="54">
         <v>90</v>
@@ -8696,19 +8693,19 @@
         <v>52</v>
       </c>
       <c r="B83" s="55" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C83" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D83" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E83" s="54">
         <v>67</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G83" s="54">
         <v>72</v>
@@ -8722,19 +8719,19 @@
         <v>53</v>
       </c>
       <c r="B84" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C84" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D84" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E84" s="54">
         <v>36</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G84" s="54">
         <v>67</v>
@@ -8748,19 +8745,19 @@
         <v>54</v>
       </c>
       <c r="B85" s="55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C85" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D85" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E85" s="54">
         <v>11</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G85" s="54">
         <v>72</v>
@@ -8774,19 +8771,19 @@
         <v>55</v>
       </c>
       <c r="B86" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C86" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D86" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E86" s="54">
         <v>110</v>
       </c>
       <c r="F86" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G86" s="54">
         <v>95</v>
@@ -8800,19 +8797,19 @@
         <v>56</v>
       </c>
       <c r="B87" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C87" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D87" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E87" s="54">
         <v>80</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G87" s="54">
         <v>72</v>
@@ -8826,19 +8823,19 @@
         <v>57</v>
       </c>
       <c r="B88" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C88" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D88" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E88" s="54">
         <v>70</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G88" s="54">
         <v>90</v>
@@ -8852,19 +8849,19 @@
         <v>58</v>
       </c>
       <c r="B89" s="55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C89" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D89" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E89" s="54">
         <v>107</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G89" s="54">
         <v>95</v>
@@ -8878,19 +8875,19 @@
         <v>59</v>
       </c>
       <c r="B90" s="55" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C90" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D90" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E90" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F90" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G90" s="54">
         <v>72</v>
@@ -8904,19 +8901,19 @@
         <v>60</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C91" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D91" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E91" s="54">
         <v>70</v>
       </c>
       <c r="F91" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G91" s="54">
         <v>65</v>
@@ -8930,19 +8927,19 @@
         <v>61</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C92" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D92" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E92" s="54">
         <v>62</v>
       </c>
       <c r="F92" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G92" s="54">
         <v>90</v>
@@ -8956,19 +8953,19 @@
         <v>62</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C93" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D93" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E93" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F93" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E93" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F93" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G93" s="54">
         <v>68</v>
@@ -8982,19 +8979,19 @@
         <v>63</v>
       </c>
       <c r="B94" s="55" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C94" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D94" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E94" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F94" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E94" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F94" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G94" s="54">
         <v>68</v>
@@ -9008,19 +9005,19 @@
         <v>64</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C95" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D95" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E95" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F95" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E95" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F95" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G95" s="54">
         <v>70</v>
@@ -9034,19 +9031,19 @@
         <v>65</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C96" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E96" s="54">
         <v>100</v>
       </c>
       <c r="F96" s="54" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G96" s="54">
         <v>95</v>
@@ -9060,19 +9057,19 @@
         <v>66</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C97" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E97" s="54">
         <v>60</v>
       </c>
       <c r="F97" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G97" s="54">
         <v>90</v>
@@ -9086,19 +9083,19 @@
         <v>67</v>
       </c>
       <c r="B98" s="55" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C98" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E98" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F98" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G98" s="54">
         <v>63</v>
@@ -9112,19 +9109,19 @@
         <v>68</v>
       </c>
       <c r="B99" s="55" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C99" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E99" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F99" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G99" s="54">
         <v>72</v>
@@ -9138,19 +9135,19 @@
         <v>69</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C100" s="54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E100" s="54">
         <v>40</v>
       </c>
       <c r="F100" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G100" s="54">
         <v>64</v>
@@ -9164,19 +9161,19 @@
         <v>70</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C101" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E101" s="54">
         <v>67</v>
       </c>
       <c r="F101" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G101" s="54">
         <v>72</v>
@@ -9190,19 +9187,19 @@
         <v>71</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C102" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E102" s="54">
         <v>70</v>
       </c>
       <c r="F102" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G102" s="54">
         <v>62</v>
@@ -9216,19 +9213,19 @@
         <v>72</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C103" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D103" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E103" s="54">
         <v>100</v>
       </c>
       <c r="F103" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G103" s="54">
         <v>95</v>
@@ -9242,19 +9239,19 @@
         <v>73</v>
       </c>
       <c r="B104" s="55" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C104" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D104" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E104" s="54">
         <v>55</v>
       </c>
       <c r="F104" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G104" s="54">
         <v>90</v>
@@ -9268,19 +9265,19 @@
         <v>74</v>
       </c>
       <c r="B105" s="55" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C105" s="54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D105" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E105" s="54">
         <v>57</v>
       </c>
       <c r="F105" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G105" s="54">
         <v>63</v>
@@ -9294,19 +9291,19 @@
         <v>75</v>
       </c>
       <c r="B106" s="55" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C106" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D106" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E106" s="54">
         <v>40</v>
       </c>
       <c r="F106" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G106" s="54">
         <v>65</v>
@@ -9320,19 +9317,19 @@
         <v>76</v>
       </c>
       <c r="B107" s="55" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C107" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D107" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E107" s="54">
         <v>80</v>
       </c>
       <c r="F107" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G107" s="54">
         <v>72</v>
@@ -9346,19 +9343,19 @@
         <v>77</v>
       </c>
       <c r="B108" s="55" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C108" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D108" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E108" s="54">
         <v>100</v>
       </c>
       <c r="F108" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G108" s="54">
         <v>95</v>
@@ -9372,19 +9369,19 @@
         <v>78</v>
       </c>
       <c r="B109" s="55" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C109" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D109" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E109" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F109" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G109" s="54">
         <v>72</v>
@@ -9398,19 +9395,19 @@
         <v>79</v>
       </c>
       <c r="B110" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C110" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D110" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E110" s="54">
         <v>66</v>
       </c>
       <c r="F110" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G110" s="54">
         <v>65</v>
@@ -9424,19 +9421,19 @@
         <v>80</v>
       </c>
       <c r="B111" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C111" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D111" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E111" s="54">
         <v>54</v>
       </c>
       <c r="F111" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G111" s="54">
         <v>90</v>
@@ -9450,19 +9447,19 @@
         <v>81</v>
       </c>
       <c r="B112" s="55" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C112" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D112" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E112" s="54">
         <v>7</v>
       </c>
       <c r="F112" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G112" s="54">
         <v>63</v>
@@ -9476,19 +9473,19 @@
         <v>82</v>
       </c>
       <c r="B113" s="55" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C113" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D113" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E113" s="54">
         <v>1</v>
       </c>
       <c r="F113" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G113" s="54">
         <v>63</v>
@@ -9502,19 +9499,19 @@
         <v>83</v>
       </c>
       <c r="B114" s="55" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C114" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D114" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E114" s="54">
         <v>300</v>
       </c>
       <c r="F114" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G114" s="54">
         <v>90</v>
@@ -9528,19 +9525,19 @@
         <v>84</v>
       </c>
       <c r="B115" s="55" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C115" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D115" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E115" s="54">
         <v>50</v>
       </c>
       <c r="F115" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G115" s="54">
         <v>90</v>
@@ -9554,19 +9551,19 @@
         <v>85</v>
       </c>
       <c r="B116" s="55" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C116" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D116" s="55" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E116" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F116" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G116" s="54">
         <v>72</v>
@@ -9580,19 +9577,19 @@
         <v>86</v>
       </c>
       <c r="B117" s="55" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C117" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D117" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E117" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F117" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G117" s="54">
         <v>63</v>
@@ -9606,19 +9603,19 @@
         <v>87</v>
       </c>
       <c r="B118" s="55" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C118" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D118" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E118" s="54">
         <v>250</v>
       </c>
       <c r="F118" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G118" s="54">
         <v>90</v>
@@ -9632,19 +9629,19 @@
         <v>88</v>
       </c>
       <c r="B119" s="55" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C119" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D119" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E119" s="54">
         <v>12</v>
       </c>
       <c r="F119" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G119" s="54">
         <v>65</v>
@@ -9658,19 +9655,19 @@
         <v>89</v>
       </c>
       <c r="B120" s="55" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C120" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D120" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E120" s="54">
         <v>67</v>
       </c>
       <c r="F120" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G120" s="54">
         <v>72</v>
@@ -9684,19 +9681,19 @@
         <v>90</v>
       </c>
       <c r="B121" s="55" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C121" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D121" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E121" s="54">
         <v>15</v>
       </c>
       <c r="F121" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G121" s="54">
         <v>62</v>
@@ -9710,19 +9707,19 @@
         <v>91</v>
       </c>
       <c r="B122" s="55" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C122" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D122" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E122" s="54">
         <v>50</v>
       </c>
       <c r="F122" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G122" s="54">
         <v>90</v>
@@ -9736,19 +9733,19 @@
         <v>92</v>
       </c>
       <c r="B123" s="55" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C123" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D123" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E123" s="54">
         <v>6</v>
       </c>
       <c r="F123" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G123" s="54">
         <v>65</v>
@@ -9762,19 +9759,19 @@
         <v>93</v>
       </c>
       <c r="B124" s="55" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C124" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D124" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E124" s="54">
         <v>200</v>
       </c>
       <c r="F124" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G124" s="54">
         <v>90</v>
@@ -9788,19 +9785,19 @@
         <v>94</v>
       </c>
       <c r="B125" s="55" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C125" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D125" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E125" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F125" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G125" s="54">
         <v>72</v>
@@ -9814,19 +9811,19 @@
         <v>95</v>
       </c>
       <c r="B126" s="55" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C126" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D126" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E126" s="54">
         <v>600</v>
       </c>
       <c r="F126" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G126" s="54">
         <v>85</v>
@@ -9840,19 +9837,19 @@
         <v>96</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C127" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D127" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E127" s="54">
         <v>5</v>
       </c>
       <c r="F127" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G127" s="54">
         <v>63</v>
@@ -9866,19 +9863,19 @@
         <v>97</v>
       </c>
       <c r="B128" s="55" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C128" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D128" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E128" s="54">
         <v>80</v>
       </c>
       <c r="F128" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G128" s="54">
         <v>72</v>
@@ -9892,19 +9889,19 @@
         <v>98</v>
       </c>
       <c r="B129" s="55" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C129" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D129" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E129" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F129" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G129" s="54">
         <v>63</v>
@@ -9918,19 +9915,19 @@
         <v>99</v>
       </c>
       <c r="B130" s="55" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C130" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D130" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E130" s="54">
         <v>180</v>
       </c>
       <c r="F130" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G130" s="54">
         <v>90</v>
@@ -9944,19 +9941,19 @@
         <v>100</v>
       </c>
       <c r="B131" s="55" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C131" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D131" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E131" s="54">
         <v>136</v>
       </c>
       <c r="F131" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G131" s="54">
         <v>85</v>
@@ -9997,7 +9994,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -10007,27 +10004,27 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -10037,17 +10034,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -10057,37 +10054,37 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -10097,22 +10094,22 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -10122,27 +10119,27 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -10152,17 +10149,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
+++ b/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="521">
   <si>
     <t>ProofLoop タスクシート 2026-08 → 2027-01（最終更新 2026-08-11）</t>
   </si>
@@ -335,7 +335,10 @@
     <t>【公開前ゲート】claimトークンがGA4に送信されるのを止める</t>
   </si>
   <si>
-    <t>/claim・/invite のURLを丸めてから送信。**発行前に必須**</t>
+    <t>/claim・/invite のURLを丸めてから送信。**発行前に必須**。コード対応済み（2026-08-12）。残：実プロパティでの再検証・GA4管理画面の拡張計測機能確認（オーナー・docs/owner-todo.md）</t>
+  </si>
+  <si>
+    <t>🟡 コード完了・オーナー確認待ち</t>
   </si>
   <si>
     <t>B19</t>
@@ -3485,7 +3488,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -3502,13 +3505,13 @@
     </row>
     <row r="29" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>38</v>
@@ -3517,7 +3520,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
@@ -3543,13 +3546,13 @@
     </row>
     <row r="30" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>38</v>
@@ -3558,7 +3561,7 @@
         <v>49</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
@@ -3584,13 +3587,13 @@
     </row>
     <row r="31" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>38</v>
@@ -3599,7 +3602,7 @@
         <v>49</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
@@ -3625,13 +3628,13 @@
     </row>
     <row r="32" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>30</v>
@@ -3640,7 +3643,7 @@
         <v>25</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G32" s="14">
         <v>1</v>
@@ -3666,22 +3669,22 @@
     </row>
     <row r="33" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
@@ -3707,22 +3710,22 @@
     </row>
     <row r="34" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G34" s="14">
         <v>2</v>
@@ -3748,22 +3751,22 @@
     </row>
     <row r="35" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G35" s="14">
         <v>2</v>
@@ -3789,22 +3792,22 @@
     </row>
     <row r="36" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G36" s="14">
         <v>2</v>
@@ -3830,13 +3833,13 @@
     </row>
     <row r="37" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>30</v>
@@ -3845,7 +3848,7 @@
         <v>25</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G37" s="14">
         <v>2</v>
@@ -3871,22 +3874,22 @@
     </row>
     <row r="38" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G38" s="14">
         <v>3</v>
@@ -3912,22 +3915,22 @@
     </row>
     <row r="39" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G39" s="14">
         <v>4</v>
@@ -3953,22 +3956,22 @@
     </row>
     <row r="40" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G40" s="14">
         <v>5</v>
@@ -3994,22 +3997,22 @@
     </row>
     <row r="41" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G41" s="14">
         <v>6</v>
@@ -4035,22 +4038,22 @@
     </row>
     <row r="42" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G42" s="14">
         <v>7</v>
@@ -4076,22 +4079,22 @@
     </row>
     <row r="43" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G43" s="14">
         <v>9</v>
@@ -4117,22 +4120,22 @@
     </row>
     <row r="44" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G44" s="14">
         <v>11</v>
@@ -4158,22 +4161,22 @@
     </row>
     <row r="45" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G45" s="14">
         <v>3</v>
@@ -4199,22 +4202,22 @@
     </row>
     <row r="46" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G46" s="14">
         <v>9</v>
@@ -4240,22 +4243,22 @@
     </row>
     <row r="47" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G47" s="14">
         <v>11</v>
@@ -4281,13 +4284,13 @@
     </row>
     <row r="48" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>38</v>
@@ -4296,7 +4299,7 @@
         <v>25</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G48" s="14">
         <v>1</v>
@@ -4322,13 +4325,13 @@
     </row>
     <row r="49" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>38</v>
@@ -4337,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G49" s="14">
         <v>2</v>
@@ -4363,13 +4366,13 @@
     </row>
     <row r="50" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>38</v>
@@ -4378,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G50" s="14">
         <v>1</v>
@@ -4404,22 +4407,22 @@
     </row>
     <row r="51" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G51" s="14">
         <v>5</v>
@@ -4445,22 +4448,22 @@
     </row>
     <row r="52" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G52" s="14">
         <v>5</v>
@@ -4486,13 +4489,13 @@
     </row>
     <row r="53" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>38</v>
@@ -4501,7 +4504,7 @@
         <v>25</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G53" s="14">
         <v>3</v>
@@ -4527,13 +4530,13 @@
     </row>
     <row r="54" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>38</v>
@@ -4542,7 +4545,7 @@
         <v>25</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G54" s="14">
         <v>1</v>
@@ -4568,13 +4571,13 @@
     </row>
     <row r="55" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>24</v>
@@ -4583,7 +4586,7 @@
         <v>25</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G55" s="14">
         <v>1</v>
@@ -4609,13 +4612,13 @@
     </row>
     <row r="56" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>38</v>
@@ -4624,7 +4627,7 @@
         <v>49</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G56" s="14">
         <v>1</v>
@@ -4650,13 +4653,13 @@
     </row>
     <row r="57" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>38</v>
@@ -4665,7 +4668,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G57" s="14">
         <v>1</v>
@@ -4691,13 +4694,13 @@
     </row>
     <row r="58" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>38</v>
@@ -4706,7 +4709,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G58" s="14">
         <v>3</v>
@@ -4732,22 +4735,22 @@
     </row>
     <row r="59" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G59" s="14">
         <v>1</v>
@@ -4773,13 +4776,13 @@
     </row>
     <row r="60" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>38</v>
@@ -4788,7 +4791,7 @@
         <v>25</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G60" s="14">
         <v>2</v>
@@ -4814,22 +4817,22 @@
     </row>
     <row r="61" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G61" s="14">
         <v>3</v>
@@ -4855,13 +4858,13 @@
     </row>
     <row r="62" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>38</v>
@@ -4870,7 +4873,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G62" s="14">
         <v>5</v>
@@ -4896,13 +4899,13 @@
     </row>
     <row r="63" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>38</v>
@@ -4911,7 +4914,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G63" s="14">
         <v>7</v>
@@ -4937,13 +4940,13 @@
     </row>
     <row r="64" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>38</v>
@@ -4952,7 +4955,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G64" s="14">
         <v>9</v>
@@ -4978,13 +4981,13 @@
     </row>
     <row r="65" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>38</v>
@@ -4993,7 +4996,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G65" s="14">
         <v>11</v>
@@ -5019,13 +5022,13 @@
     </row>
     <row r="66" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>38</v>
@@ -5034,7 +5037,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G66" s="14">
         <v>3</v>
@@ -5060,13 +5063,13 @@
     </row>
     <row r="67" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>30</v>
@@ -5075,7 +5078,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G67" s="14">
         <v>1</v>
@@ -5101,22 +5104,22 @@
     </row>
     <row r="68" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G68" s="14">
         <v>4</v>
@@ -5142,22 +5145,22 @@
     </row>
     <row r="69" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G69" s="14">
         <v>4</v>
@@ -5183,13 +5186,13 @@
     </row>
     <row r="70" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>30</v>
@@ -5198,7 +5201,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G70" s="14">
         <v>1</v>
@@ -5224,13 +5227,13 @@
     </row>
     <row r="71" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>30</v>
@@ -5239,7 +5242,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G71" s="14">
         <v>1</v>
@@ -5265,13 +5268,13 @@
     </row>
     <row r="72" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>30</v>
@@ -5280,7 +5283,7 @@
         <v>25</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G72" s="14">
         <v>1</v>
@@ -5306,13 +5309,13 @@
     </row>
     <row r="73" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>30</v>
@@ -5321,7 +5324,7 @@
         <v>25</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G73" s="14">
         <v>5</v>
@@ -5347,13 +5350,13 @@
     </row>
     <row r="74" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>30</v>
@@ -5362,7 +5365,7 @@
         <v>21</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G74" s="14">
         <v>3</v>
@@ -5388,22 +5391,22 @@
     </row>
     <row r="75" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G75" s="14">
         <v>1</v>
@@ -5429,22 +5432,22 @@
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -5502,41 +5505,41 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5544,7 +5547,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C5" s="31">
         <v>200</v>
@@ -5573,7 +5576,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6" s="31">
         <v>350</v>
@@ -5602,7 +5605,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C7" s="31">
         <v>350</v>
@@ -5631,7 +5634,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8" s="31">
         <v>250</v>
@@ -5660,7 +5663,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C9" s="31">
         <v>150</v>
@@ -5689,7 +5692,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C10" s="31">
         <v>100</v>
@@ -5715,7 +5718,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5728,13 +5731,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D14" s="39"/>
       <c r="E14" s="39"/>
@@ -5745,13 +5748,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
@@ -5762,13 +5765,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
@@ -5779,13 +5782,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
@@ -5796,13 +5799,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -5813,7 +5816,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -5826,11 +5829,11 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -5841,11 +5844,11 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="41" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
@@ -5856,7 +5859,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -5899,17 +5902,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5931,10 +5934,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
@@ -5947,7 +5950,7 @@
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
       <c r="N5" s="44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -5955,10 +5958,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="43"/>
       <c r="E6" s="43"/>
@@ -5971,7 +5974,7 @@
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
       <c r="N6" s="44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -5979,10 +5982,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
@@ -5995,7 +5998,7 @@
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
       <c r="N7" s="44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6003,10 +6006,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D8" s="43"/>
       <c r="E8" s="43"/>
@@ -6019,7 +6022,7 @@
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
       <c r="N8" s="44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -6027,10 +6030,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
@@ -6043,7 +6046,7 @@
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
       <c r="N9" s="45" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -6051,10 +6054,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D10" s="43"/>
       <c r="E10" s="43"/>
@@ -6067,7 +6070,7 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" s="45" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -6075,10 +6078,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
@@ -6091,7 +6094,7 @@
       <c r="L11" s="43"/>
       <c r="M11" s="43"/>
       <c r="N11" s="45" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -6099,10 +6102,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D12" s="43"/>
       <c r="E12" s="43"/>
@@ -6115,7 +6118,7 @@
       <c r="L12" s="43"/>
       <c r="M12" s="43"/>
       <c r="N12" s="45" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -6123,10 +6126,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
@@ -6139,12 +6142,12 @@
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
       <c r="N13" s="47" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6163,49 +6166,49 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -6970,12 +6973,12 @@
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -7025,17 +7028,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7047,14 +7050,14 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="47">
         <v>30</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
@@ -7063,14 +7066,14 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="47">
         <v>25</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="43"/>
@@ -7079,14 +7082,14 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="47">
         <v>25</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E7" s="43"/>
       <c r="F7" s="43"/>
@@ -7095,14 +7098,14 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="47">
         <v>20</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E8" s="43"/>
       <c r="F8" s="43"/>
@@ -7111,7 +7114,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -7123,7 +7126,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B11" s="50"/>
       <c r="C11" s="50"/>
@@ -7135,7 +7138,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -7147,22 +7150,22 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B15" s="52" t="s">
         <v>2</v>
@@ -7171,7 +7174,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F15" s="52">
         <v>37</v>
@@ -7179,7 +7182,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B16" s="52" t="s">
         <v>3</v>
@@ -7188,7 +7191,7 @@
         <v>350</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F16" s="52">
         <v>36</v>
@@ -7196,7 +7199,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="52" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B17" s="52" t="s">
         <v>4</v>
@@ -7205,7 +7208,7 @@
         <v>350</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F17" s="52">
         <v>24</v>
@@ -7213,7 +7216,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B18" s="52" t="s">
         <v>5</v>
@@ -7222,7 +7225,7 @@
         <v>250</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F18" s="52">
         <v>15</v>
@@ -7230,7 +7233,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="52" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B19" s="52" t="s">
         <v>6</v>
@@ -7239,7 +7242,7 @@
         <v>150</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F19" s="52">
         <v>14</v>
@@ -7247,7 +7250,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B20" s="52" t="s">
         <v>7</v>
@@ -7256,7 +7259,7 @@
         <v>100</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F20" s="52">
         <v>12</v>
@@ -7264,13 +7267,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C21" s="47">
         <v>1400</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F21" s="52">
         <v>11</v>
@@ -7278,7 +7281,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="49" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F22" s="52">
         <v>11</v>
@@ -7286,7 +7289,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="49" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F23" s="52">
         <v>10</v>
@@ -7294,7 +7297,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="49" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F24" s="52">
         <v>10</v>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="49" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F25" s="52">
         <v>10</v>
@@ -7310,7 +7313,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="49" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F26" s="52">
         <v>5</v>
@@ -7318,7 +7321,7 @@
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="49" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F27" s="52">
         <v>5</v>
@@ -7326,7 +7329,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -7338,28 +7341,28 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -7367,19 +7370,19 @@
         <v>1</v>
       </c>
       <c r="B32" s="55" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E32" s="54">
         <v>257</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G32" s="54">
         <v>100</v>
@@ -7393,19 +7396,19 @@
         <v>2</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E33" s="54">
         <v>200</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G33" s="54">
         <v>95</v>
@@ -7419,19 +7422,19 @@
         <v>3</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C34" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E34" s="54">
         <v>200</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G34" s="54">
         <v>77</v>
@@ -7445,19 +7448,19 @@
         <v>4</v>
       </c>
       <c r="B35" s="55" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E35" s="54">
         <v>2716</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G35" s="54">
         <v>95</v>
@@ -7471,19 +7474,19 @@
         <v>5</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E36" s="54">
         <v>150</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G36" s="54">
         <v>95</v>
@@ -7497,19 +7500,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C37" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E37" s="54">
         <v>190</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G37" s="54">
         <v>80</v>
@@ -7523,19 +7526,19 @@
         <v>7</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E38" s="54">
         <v>150</v>
       </c>
       <c r="F38" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G38" s="54">
         <v>80</v>
@@ -7549,19 +7552,19 @@
         <v>8</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E39" s="54">
         <v>2170</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G39" s="54">
         <v>95</v>
@@ -7575,19 +7578,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E40" s="54">
         <v>22</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G40" s="54">
         <v>77</v>
@@ -7601,19 +7604,19 @@
         <v>10</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E41" s="54">
         <v>140</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G41" s="54">
         <v>95</v>
@@ -7627,19 +7630,19 @@
         <v>11</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E42" s="54">
         <v>60</v>
       </c>
       <c r="F42" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G42" s="54">
         <v>73</v>
@@ -7653,19 +7656,19 @@
         <v>12</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E43" s="54">
         <v>54</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G43" s="54">
         <v>73</v>
@@ -7679,19 +7682,19 @@
         <v>13</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C44" s="54" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E44" s="54">
         <v>39</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G44" s="54">
         <v>68</v>
@@ -7705,19 +7708,19 @@
         <v>14</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D45" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E45" s="54">
         <v>108</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G45" s="54">
         <v>77</v>
@@ -7731,19 +7734,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="55" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C46" s="54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D46" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E46" s="54">
         <v>60</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G46" s="54">
         <v>67</v>
@@ -7757,19 +7760,19 @@
         <v>16</v>
       </c>
       <c r="B47" s="55" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D47" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E47" s="54">
         <v>80</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G47" s="54">
         <v>72</v>
@@ -7783,19 +7786,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="55" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C48" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E48" s="54">
         <v>200</v>
       </c>
       <c r="F48" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G48" s="54">
         <v>95</v>
@@ -7809,19 +7812,19 @@
         <v>18</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D49" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E49" s="54">
         <v>125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G49" s="54">
         <v>95</v>
@@ -7835,19 +7838,19 @@
         <v>19</v>
       </c>
       <c r="B50" s="55" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C50" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D50" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E50" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F50" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G50" s="54">
         <v>77</v>
@@ -7861,19 +7864,19 @@
         <v>20</v>
       </c>
       <c r="B51" s="55" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D51" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E51" s="54">
         <v>200</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G51" s="54">
         <v>75</v>
@@ -7887,19 +7890,19 @@
         <v>21</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E52" s="54">
         <v>165</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G52" s="54">
         <v>95</v>
@@ -7913,19 +7916,19 @@
         <v>22</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E53" s="54">
         <v>70</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G53" s="54">
         <v>75</v>
@@ -7939,19 +7942,19 @@
         <v>23</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E54" s="54">
         <v>100</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G54" s="54">
         <v>95</v>
@@ -7965,19 +7968,19 @@
         <v>24</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E55" s="54">
         <v>158</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G55" s="54">
         <v>95</v>
@@ -7991,19 +7994,19 @@
         <v>25</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D56" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E56" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F56" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G56" s="54">
         <v>77</v>
@@ -8017,19 +8020,19 @@
         <v>26</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E57" s="54">
         <v>96</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G57" s="54">
         <v>90</v>
@@ -8043,19 +8046,19 @@
         <v>27</v>
       </c>
       <c r="B58" s="55" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C58" s="54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E58" s="54">
         <v>120</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G58" s="54">
         <v>68</v>
@@ -8069,19 +8072,19 @@
         <v>28</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E59" s="54">
         <v>41</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G59" s="54">
         <v>68</v>
@@ -8095,19 +8098,19 @@
         <v>29</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C60" s="54" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D60" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E60" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F60" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G60" s="54">
         <v>68</v>
@@ -8121,19 +8124,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="55" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C61" s="54" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D61" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E61" s="54">
         <v>40</v>
       </c>
       <c r="F61" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G61" s="54">
         <v>69</v>
@@ -8147,19 +8150,19 @@
         <v>31</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C62" s="54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D62" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E62" s="54">
         <v>67</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G62" s="54">
         <v>72</v>
@@ -8173,19 +8176,19 @@
         <v>32</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C63" s="54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E63" s="54">
         <v>60</v>
       </c>
       <c r="F63" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G63" s="54">
         <v>67</v>
@@ -8199,19 +8202,19 @@
         <v>33</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C64" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E64" s="54">
         <v>150</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G64" s="54">
         <v>95</v>
@@ -8225,19 +8228,19 @@
         <v>34</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C65" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E65" s="54">
         <v>89</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G65" s="54">
         <v>90</v>
@@ -8251,19 +8254,19 @@
         <v>35</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D66" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E66" s="54">
         <v>57</v>
       </c>
       <c r="F66" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G66" s="54">
         <v>63</v>
@@ -8277,19 +8280,19 @@
         <v>36</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C67" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E67" s="54">
         <v>54</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G67" s="54">
         <v>75</v>
@@ -8303,19 +8306,19 @@
         <v>37</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C68" s="54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E68" s="54">
         <v>80</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G68" s="54">
         <v>72</v>
@@ -8329,19 +8332,19 @@
         <v>38</v>
       </c>
       <c r="B69" s="55" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C69" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D69" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E69" s="54">
         <v>200</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G69" s="54">
         <v>72</v>
@@ -8355,19 +8358,19 @@
         <v>39</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C70" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D70" s="55" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E70" s="54">
         <v>1000</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G70" s="54">
         <v>70</v>
@@ -8381,19 +8384,19 @@
         <v>40</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D71" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E71" s="54">
         <v>120</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G71" s="54">
         <v>95</v>
@@ -8407,19 +8410,19 @@
         <v>41</v>
       </c>
       <c r="B72" s="55" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C72" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D72" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E72" s="54">
         <v>83</v>
       </c>
       <c r="F72" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G72" s="54">
         <v>90</v>
@@ -8433,19 +8436,19 @@
         <v>42</v>
       </c>
       <c r="B73" s="55" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C73" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D73" s="55" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E73" s="54">
         <v>120</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G73" s="54">
         <v>95</v>
@@ -8459,19 +8462,19 @@
         <v>43</v>
       </c>
       <c r="B74" s="55" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C74" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D74" s="55" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E74" s="54">
         <v>50</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G74" s="54">
         <v>72</v>
@@ -8485,19 +8488,19 @@
         <v>44</v>
       </c>
       <c r="B75" s="55" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C75" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D75" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E75" s="54">
         <v>80</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G75" s="54">
         <v>90</v>
@@ -8511,19 +8514,19 @@
         <v>45</v>
       </c>
       <c r="B76" s="55" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C76" s="54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D76" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E76" s="54">
         <v>49</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G76" s="54">
         <v>68</v>
@@ -8537,19 +8540,19 @@
         <v>46</v>
       </c>
       <c r="B77" s="55" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C77" s="54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D77" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E77" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F77" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G77" s="54">
         <v>68</v>
@@ -8563,19 +8566,19 @@
         <v>47</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C78" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E78" s="54">
         <v>200</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G78" s="54">
         <v>70</v>
@@ -8589,19 +8592,19 @@
         <v>48</v>
       </c>
       <c r="B79" s="55" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C79" s="54" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D79" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E79" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G79" s="54">
         <v>63</v>
@@ -8615,19 +8618,19 @@
         <v>49</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C80" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E80" s="54">
         <v>120</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G80" s="54">
         <v>95</v>
@@ -8641,19 +8644,19 @@
         <v>50</v>
       </c>
       <c r="B81" s="55" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C81" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D81" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E81" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F81" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G81" s="54">
         <v>70</v>
@@ -8667,19 +8670,19 @@
         <v>51</v>
       </c>
       <c r="B82" s="55" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C82" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E82" s="54">
         <v>80</v>
       </c>
       <c r="F82" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G82" s="54">
         <v>90</v>
@@ -8693,19 +8696,19 @@
         <v>52</v>
       </c>
       <c r="B83" s="55" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C83" s="54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D83" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E83" s="54">
         <v>67</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G83" s="54">
         <v>72</v>
@@ -8719,19 +8722,19 @@
         <v>53</v>
       </c>
       <c r="B84" s="55" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C84" s="54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D84" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E84" s="54">
         <v>36</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G84" s="54">
         <v>67</v>
@@ -8745,19 +8748,19 @@
         <v>54</v>
       </c>
       <c r="B85" s="55" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C85" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D85" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E85" s="54">
         <v>11</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G85" s="54">
         <v>72</v>
@@ -8771,19 +8774,19 @@
         <v>55</v>
       </c>
       <c r="B86" s="55" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C86" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D86" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E86" s="54">
         <v>110</v>
       </c>
       <c r="F86" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G86" s="54">
         <v>95</v>
@@ -8797,19 +8800,19 @@
         <v>56</v>
       </c>
       <c r="B87" s="55" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C87" s="54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D87" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E87" s="54">
         <v>80</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G87" s="54">
         <v>72</v>
@@ -8823,19 +8826,19 @@
         <v>57</v>
       </c>
       <c r="B88" s="55" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C88" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D88" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E88" s="54">
         <v>70</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G88" s="54">
         <v>90</v>
@@ -8849,19 +8852,19 @@
         <v>58</v>
       </c>
       <c r="B89" s="55" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C89" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D89" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E89" s="54">
         <v>107</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G89" s="54">
         <v>95</v>
@@ -8875,19 +8878,19 @@
         <v>59</v>
       </c>
       <c r="B90" s="55" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C90" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D90" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E90" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F90" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G90" s="54">
         <v>72</v>
@@ -8901,19 +8904,19 @@
         <v>60</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C91" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D91" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E91" s="54">
         <v>70</v>
       </c>
       <c r="F91" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G91" s="54">
         <v>65</v>
@@ -8927,19 +8930,19 @@
         <v>61</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C92" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D92" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E92" s="54">
         <v>62</v>
       </c>
       <c r="F92" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G92" s="54">
         <v>90</v>
@@ -8953,19 +8956,19 @@
         <v>62</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C93" s="54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D93" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E93" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F93" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G93" s="54">
         <v>68</v>
@@ -8979,19 +8982,19 @@
         <v>63</v>
       </c>
       <c r="B94" s="55" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C94" s="54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E94" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F94" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G94" s="54">
         <v>68</v>
@@ -9005,19 +9008,19 @@
         <v>64</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C95" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D95" s="55" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E95" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F95" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G95" s="54">
         <v>70</v>
@@ -9031,19 +9034,19 @@
         <v>65</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C96" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E96" s="54">
         <v>100</v>
       </c>
       <c r="F96" s="54" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G96" s="54">
         <v>95</v>
@@ -9057,19 +9060,19 @@
         <v>66</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C97" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E97" s="54">
         <v>60</v>
       </c>
       <c r="F97" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G97" s="54">
         <v>90</v>
@@ -9083,19 +9086,19 @@
         <v>67</v>
       </c>
       <c r="B98" s="55" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C98" s="54" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E98" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F98" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G98" s="54">
         <v>63</v>
@@ -9109,19 +9112,19 @@
         <v>68</v>
       </c>
       <c r="B99" s="55" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C99" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E99" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F99" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G99" s="54">
         <v>72</v>
@@ -9135,19 +9138,19 @@
         <v>69</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C100" s="54" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E100" s="54">
         <v>40</v>
       </c>
       <c r="F100" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G100" s="54">
         <v>64</v>
@@ -9161,19 +9164,19 @@
         <v>70</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C101" s="54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E101" s="54">
         <v>67</v>
       </c>
       <c r="F101" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G101" s="54">
         <v>72</v>
@@ -9187,19 +9190,19 @@
         <v>71</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C102" s="54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E102" s="54">
         <v>70</v>
       </c>
       <c r="F102" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G102" s="54">
         <v>62</v>
@@ -9213,19 +9216,19 @@
         <v>72</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C103" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D103" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E103" s="54">
         <v>100</v>
       </c>
       <c r="F103" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G103" s="54">
         <v>95</v>
@@ -9239,19 +9242,19 @@
         <v>73</v>
       </c>
       <c r="B104" s="55" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C104" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D104" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E104" s="54">
         <v>55</v>
       </c>
       <c r="F104" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G104" s="54">
         <v>90</v>
@@ -9265,19 +9268,19 @@
         <v>74</v>
       </c>
       <c r="B105" s="55" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C105" s="54" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D105" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E105" s="54">
         <v>57</v>
       </c>
       <c r="F105" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G105" s="54">
         <v>63</v>
@@ -9291,19 +9294,19 @@
         <v>75</v>
       </c>
       <c r="B106" s="55" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C106" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D106" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E106" s="54">
         <v>40</v>
       </c>
       <c r="F106" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G106" s="54">
         <v>65</v>
@@ -9317,19 +9320,19 @@
         <v>76</v>
       </c>
       <c r="B107" s="55" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C107" s="54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D107" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E107" s="54">
         <v>80</v>
       </c>
       <c r="F107" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G107" s="54">
         <v>72</v>
@@ -9343,19 +9346,19 @@
         <v>77</v>
       </c>
       <c r="B108" s="55" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C108" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D108" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E108" s="54">
         <v>100</v>
       </c>
       <c r="F108" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G108" s="54">
         <v>95</v>
@@ -9369,19 +9372,19 @@
         <v>78</v>
       </c>
       <c r="B109" s="55" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C109" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D109" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E109" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F109" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G109" s="54">
         <v>72</v>
@@ -9395,19 +9398,19 @@
         <v>79</v>
       </c>
       <c r="B110" s="55" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C110" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D110" s="55" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E110" s="54">
         <v>66</v>
       </c>
       <c r="F110" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G110" s="54">
         <v>65</v>
@@ -9421,19 +9424,19 @@
         <v>80</v>
       </c>
       <c r="B111" s="55" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C111" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D111" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E111" s="54">
         <v>54</v>
       </c>
       <c r="F111" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G111" s="54">
         <v>90</v>
@@ -9447,19 +9450,19 @@
         <v>81</v>
       </c>
       <c r="B112" s="55" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C112" s="54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D112" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E112" s="54">
         <v>7</v>
       </c>
       <c r="F112" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G112" s="54">
         <v>63</v>
@@ -9473,19 +9476,19 @@
         <v>82</v>
       </c>
       <c r="B113" s="55" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C113" s="54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D113" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E113" s="54">
         <v>1</v>
       </c>
       <c r="F113" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G113" s="54">
         <v>63</v>
@@ -9499,19 +9502,19 @@
         <v>83</v>
       </c>
       <c r="B114" s="55" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C114" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D114" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E114" s="54">
         <v>300</v>
       </c>
       <c r="F114" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G114" s="54">
         <v>90</v>
@@ -9525,19 +9528,19 @@
         <v>84</v>
       </c>
       <c r="B115" s="55" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C115" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D115" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E115" s="54">
         <v>50</v>
       </c>
       <c r="F115" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G115" s="54">
         <v>90</v>
@@ -9551,19 +9554,19 @@
         <v>85</v>
       </c>
       <c r="B116" s="55" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C116" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D116" s="55" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E116" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F116" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G116" s="54">
         <v>72</v>
@@ -9577,19 +9580,19 @@
         <v>86</v>
       </c>
       <c r="B117" s="55" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C117" s="54" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D117" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E117" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F117" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G117" s="54">
         <v>63</v>
@@ -9603,19 +9606,19 @@
         <v>87</v>
       </c>
       <c r="B118" s="55" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C118" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D118" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E118" s="54">
         <v>250</v>
       </c>
       <c r="F118" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G118" s="54">
         <v>90</v>
@@ -9629,19 +9632,19 @@
         <v>88</v>
       </c>
       <c r="B119" s="55" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C119" s="54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D119" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E119" s="54">
         <v>12</v>
       </c>
       <c r="F119" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G119" s="54">
         <v>65</v>
@@ -9655,19 +9658,19 @@
         <v>89</v>
       </c>
       <c r="B120" s="55" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C120" s="54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D120" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E120" s="54">
         <v>67</v>
       </c>
       <c r="F120" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G120" s="54">
         <v>72</v>
@@ -9681,19 +9684,19 @@
         <v>90</v>
       </c>
       <c r="B121" s="55" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C121" s="54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D121" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E121" s="54">
         <v>15</v>
       </c>
       <c r="F121" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G121" s="54">
         <v>62</v>
@@ -9707,19 +9710,19 @@
         <v>91</v>
       </c>
       <c r="B122" s="55" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C122" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D122" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E122" s="54">
         <v>50</v>
       </c>
       <c r="F122" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G122" s="54">
         <v>90</v>
@@ -9733,19 +9736,19 @@
         <v>92</v>
       </c>
       <c r="B123" s="55" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C123" s="54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D123" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E123" s="54">
         <v>6</v>
       </c>
       <c r="F123" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G123" s="54">
         <v>65</v>
@@ -9759,19 +9762,19 @@
         <v>93</v>
       </c>
       <c r="B124" s="55" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C124" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D124" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E124" s="54">
         <v>200</v>
       </c>
       <c r="F124" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G124" s="54">
         <v>90</v>
@@ -9785,19 +9788,19 @@
         <v>94</v>
       </c>
       <c r="B125" s="55" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C125" s="54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D125" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E125" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F125" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G125" s="54">
         <v>72</v>
@@ -9811,19 +9814,19 @@
         <v>95</v>
       </c>
       <c r="B126" s="55" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C126" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D126" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E126" s="54">
         <v>600</v>
       </c>
       <c r="F126" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G126" s="54">
         <v>85</v>
@@ -9837,19 +9840,19 @@
         <v>96</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C127" s="54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D127" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E127" s="54">
         <v>5</v>
       </c>
       <c r="F127" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G127" s="54">
         <v>63</v>
@@ -9863,19 +9866,19 @@
         <v>97</v>
       </c>
       <c r="B128" s="55" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C128" s="54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D128" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E128" s="54">
         <v>80</v>
       </c>
       <c r="F128" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G128" s="54">
         <v>72</v>
@@ -9889,19 +9892,19 @@
         <v>98</v>
       </c>
       <c r="B129" s="55" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C129" s="54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D129" s="55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E129" s="54" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F129" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G129" s="54">
         <v>63</v>
@@ -9915,19 +9918,19 @@
         <v>99</v>
       </c>
       <c r="B130" s="55" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C130" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D130" s="55" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E130" s="54">
         <v>180</v>
       </c>
       <c r="F130" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G130" s="54">
         <v>90</v>
@@ -9941,19 +9944,19 @@
         <v>100</v>
       </c>
       <c r="B131" s="55" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C131" s="54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D131" s="55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E131" s="54">
         <v>136</v>
       </c>
       <c r="F131" s="54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G131" s="54">
         <v>85</v>
@@ -9994,7 +9997,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -10004,27 +10007,27 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -10034,17 +10037,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -10054,37 +10057,37 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -10094,22 +10097,22 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -10119,27 +10122,27 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -10149,17 +10152,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
+++ b/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="520">
   <si>
     <t>ProofLoop タスクシート 2026-08 → 2027-01（最終更新 2026-08-11）</t>
   </si>
@@ -335,10 +335,7 @@
     <t>【公開前ゲート】claimトークンがGA4に送信されるのを止める</t>
   </si>
   <si>
-    <t>/claim・/invite のURLを丸めてから送信。**発行前に必須**。コード対応済み（2026-08-12）。残：実プロパティでの再検証・GA4管理画面の拡張計測機能確認（オーナー・docs/owner-todo.md）</t>
-  </si>
-  <si>
-    <t>🟡 コード完了・オーナー確認待ち</t>
+    <t>/claim・/invite のURLを丸めてから送信。コード・GA4管理画面設定・本番デプロイ・実プロパティ再検証まで完了（2026-08-12）</t>
   </si>
   <si>
     <t>B19</t>
@@ -3487,8 +3484,8 @@
       <c r="H28" s="14">
         <v>2</v>
       </c>
-      <c r="I28" s="14" t="s">
-        <v>107</v>
+      <c r="I28" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -3505,13 +3502,13 @@
     </row>
     <row r="29" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>38</v>
@@ -3520,7 +3517,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
@@ -3546,13 +3543,13 @@
     </row>
     <row r="30" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>38</v>
@@ -3561,7 +3558,7 @@
         <v>49</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
@@ -3587,13 +3584,13 @@
     </row>
     <row r="31" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>38</v>
@@ -3602,7 +3599,7 @@
         <v>49</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
@@ -3628,13 +3625,13 @@
     </row>
     <row r="32" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="C32" s="21" t="s">
         <v>118</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>119</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>30</v>
@@ -3643,7 +3640,7 @@
         <v>25</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G32" s="14">
         <v>1</v>
@@ -3669,22 +3666,22 @@
     </row>
     <row r="33" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>122</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>123</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
@@ -3710,22 +3707,22 @@
     </row>
     <row r="34" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="E34" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="13" t="s">
         <v>127</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>128</v>
       </c>
       <c r="G34" s="14">
         <v>2</v>
@@ -3751,22 +3748,22 @@
     </row>
     <row r="35" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="G35" s="14">
         <v>2</v>
@@ -3792,22 +3789,22 @@
     </row>
     <row r="36" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="21" t="s">
+      <c r="D36" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="G36" s="14">
         <v>2</v>
@@ -3833,13 +3830,13 @@
     </row>
     <row r="37" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>135</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>136</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>30</v>
@@ -3848,7 +3845,7 @@
         <v>25</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G37" s="14">
         <v>2</v>
@@ -3874,22 +3871,22 @@
     </row>
     <row r="38" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="D38" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D38" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E38" s="14" t="s">
+      <c r="F38" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>141</v>
       </c>
       <c r="G38" s="14">
         <v>3</v>
@@ -3915,22 +3912,22 @@
     </row>
     <row r="39" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="D39" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F39" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="G39" s="14">
         <v>4</v>
@@ -3956,22 +3953,22 @@
     </row>
     <row r="40" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="D40" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>146</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>147</v>
       </c>
       <c r="G40" s="14">
         <v>5</v>
@@ -3997,22 +3994,22 @@
     </row>
     <row r="41" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" s="13" t="s">
+      <c r="D41" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>149</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>150</v>
       </c>
       <c r="G41" s="14">
         <v>6</v>
@@ -4038,22 +4035,22 @@
     </row>
     <row r="42" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="13" t="s">
+      <c r="D42" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>153</v>
       </c>
       <c r="G42" s="14">
         <v>7</v>
@@ -4079,22 +4076,22 @@
     </row>
     <row r="43" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B43" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="13" t="s">
+      <c r="D43" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="G43" s="14">
         <v>9</v>
@@ -4120,22 +4117,22 @@
     </row>
     <row r="44" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="B44" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="13" t="s">
+      <c r="D44" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F44" s="13" t="s">
         <v>158</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>159</v>
       </c>
       <c r="G44" s="14">
         <v>11</v>
@@ -4161,22 +4158,22 @@
     </row>
     <row r="45" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B45" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C45" s="13" t="s">
+      <c r="D45" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>162</v>
       </c>
       <c r="G45" s="14">
         <v>3</v>
@@ -4202,22 +4199,22 @@
     </row>
     <row r="46" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>164</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G46" s="14">
         <v>9</v>
@@ -4243,22 +4240,22 @@
     </row>
     <row r="47" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>166</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>167</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G47" s="14">
         <v>11</v>
@@ -4284,13 +4281,13 @@
     </row>
     <row r="48" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="C48" s="13" t="s">
         <v>170</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>171</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>38</v>
@@ -4299,7 +4296,7 @@
         <v>25</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G48" s="14">
         <v>1</v>
@@ -4325,13 +4322,13 @@
     </row>
     <row r="49" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="B49" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>174</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>38</v>
@@ -4340,7 +4337,7 @@
         <v>25</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G49" s="14">
         <v>2</v>
@@ -4366,13 +4363,13 @@
     </row>
     <row r="50" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>177</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>38</v>
@@ -4381,7 +4378,7 @@
         <v>25</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G50" s="14">
         <v>1</v>
@@ -4407,22 +4404,22 @@
     </row>
     <row r="51" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>179</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>180</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G51" s="14">
         <v>5</v>
@@ -4448,22 +4445,22 @@
     </row>
     <row r="52" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>182</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>183</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G52" s="14">
         <v>5</v>
@@ -4489,13 +4486,13 @@
     </row>
     <row r="53" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>185</v>
-      </c>
-      <c r="B53" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>186</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>38</v>
@@ -4504,7 +4501,7 @@
         <v>25</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G53" s="14">
         <v>3</v>
@@ -4530,13 +4527,13 @@
     </row>
     <row r="54" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>188</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>189</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>38</v>
@@ -4545,7 +4542,7 @@
         <v>25</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G54" s="14">
         <v>1</v>
@@ -4571,13 +4568,13 @@
     </row>
     <row r="55" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="B55" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>192</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>24</v>
@@ -4586,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G55" s="14">
         <v>1</v>
@@ -4612,13 +4609,13 @@
     </row>
     <row r="56" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>194</v>
-      </c>
-      <c r="B56" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>195</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>38</v>
@@ -4627,7 +4624,7 @@
         <v>49</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G56" s="14">
         <v>1</v>
@@ -4653,13 +4650,13 @@
     </row>
     <row r="57" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="13" t="s">
         <v>197</v>
-      </c>
-      <c r="B57" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>198</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>38</v>
@@ -4668,7 +4665,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G57" s="14">
         <v>1</v>
@@ -4694,13 +4691,13 @@
     </row>
     <row r="58" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="B58" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>38</v>
@@ -4709,7 +4706,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G58" s="14">
         <v>3</v>
@@ -4735,22 +4732,22 @@
     </row>
     <row r="59" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="C59" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="14" t="s">
         <v>205</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>206</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G59" s="14">
         <v>1</v>
@@ -4776,13 +4773,13 @@
     </row>
     <row r="60" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>209</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>38</v>
@@ -4791,7 +4788,7 @@
         <v>25</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G60" s="14">
         <v>2</v>
@@ -4817,22 +4814,22 @@
     </row>
     <row r="61" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>211</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>212</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G61" s="14">
         <v>3</v>
@@ -4858,13 +4855,13 @@
     </row>
     <row r="62" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>38</v>
@@ -4873,7 +4870,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G62" s="14">
         <v>5</v>
@@ -4899,13 +4896,13 @@
     </row>
     <row r="63" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="B63" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>38</v>
@@ -4914,7 +4911,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G63" s="14">
         <v>7</v>
@@ -4940,13 +4937,13 @@
     </row>
     <row r="64" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="B64" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>38</v>
@@ -4955,7 +4952,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G64" s="14">
         <v>9</v>
@@ -4981,13 +4978,13 @@
     </row>
     <row r="65" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C65" s="13" t="s">
         <v>221</v>
-      </c>
-      <c r="B65" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>222</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>38</v>
@@ -4996,7 +4993,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G65" s="14">
         <v>11</v>
@@ -5022,13 +5019,13 @@
     </row>
     <row r="66" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="B66" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>38</v>
@@ -5037,7 +5034,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G66" s="14">
         <v>3</v>
@@ -5063,13 +5060,13 @@
     </row>
     <row r="67" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="C67" s="21" t="s">
         <v>227</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>228</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>30</v>
@@ -5078,7 +5075,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G67" s="14">
         <v>1</v>
@@ -5104,22 +5101,22 @@
     </row>
     <row r="68" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E68" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>232</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>233</v>
       </c>
       <c r="G68" s="14">
         <v>4</v>
@@ -5145,22 +5142,22 @@
     </row>
     <row r="69" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="B69" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>235</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G69" s="14">
         <v>4</v>
@@ -5186,13 +5183,13 @@
     </row>
     <row r="70" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>238</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>30</v>
@@ -5201,7 +5198,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G70" s="14">
         <v>1</v>
@@ -5227,13 +5224,13 @@
     </row>
     <row r="71" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C71" s="13" t="s">
         <v>240</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>30</v>
@@ -5242,7 +5239,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G71" s="14">
         <v>1</v>
@@ -5268,13 +5265,13 @@
     </row>
     <row r="72" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>244</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>30</v>
@@ -5283,7 +5280,7 @@
         <v>25</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G72" s="14">
         <v>1</v>
@@ -5309,13 +5306,13 @@
     </row>
     <row r="73" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>30</v>
@@ -5324,7 +5321,7 @@
         <v>25</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G73" s="14">
         <v>5</v>
@@ -5350,13 +5347,13 @@
     </row>
     <row r="74" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>249</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>250</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>30</v>
@@ -5365,7 +5362,7 @@
         <v>21</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G74" s="14">
         <v>3</v>
@@ -5391,22 +5388,22 @@
     </row>
     <row r="75" ht="26" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>252</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>253</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G75" s="14">
         <v>1</v>
@@ -5432,22 +5429,22 @@
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5505,41 +5502,41 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5547,7 +5544,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C5" s="31">
         <v>200</v>
@@ -5576,7 +5573,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="31">
         <v>350</v>
@@ -5605,7 +5602,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C7" s="31">
         <v>350</v>
@@ -5634,7 +5631,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C8" s="31">
         <v>250</v>
@@ -5663,7 +5660,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C9" s="31">
         <v>150</v>
@@ -5692,7 +5689,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10" s="31">
         <v>100</v>
@@ -5718,7 +5715,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5731,13 +5728,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="C14" s="39" t="s">
         <v>278</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>279</v>
       </c>
       <c r="D14" s="39"/>
       <c r="E14" s="39"/>
@@ -5748,13 +5745,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="C15" s="39" t="s">
         <v>281</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>282</v>
       </c>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
@@ -5765,13 +5762,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="B16" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="C16" s="39" t="s">
         <v>284</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>285</v>
       </c>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
@@ -5782,13 +5779,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="B17" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="C17" s="39" t="s">
         <v>287</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>288</v>
       </c>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
@@ -5799,13 +5796,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="C18" s="39" t="s">
         <v>290</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>291</v>
       </c>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -5816,7 +5813,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -5829,11 +5826,11 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -5844,11 +5841,11 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
@@ -5859,7 +5856,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -5902,17 +5899,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5934,10 +5931,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>301</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>302</v>
       </c>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
@@ -5950,7 +5947,7 @@
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
       <c r="N5" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -5958,10 +5955,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>304</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>305</v>
       </c>
       <c r="D6" s="43"/>
       <c r="E6" s="43"/>
@@ -5974,7 +5971,7 @@
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
       <c r="N6" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -5982,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>306</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>307</v>
       </c>
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
@@ -5998,7 +5995,7 @@
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
       <c r="N7" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6006,10 +6003,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>308</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>309</v>
       </c>
       <c r="D8" s="43"/>
       <c r="E8" s="43"/>
@@ -6022,7 +6019,7 @@
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
       <c r="N8" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -6030,10 +6027,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>310</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>311</v>
       </c>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
@@ -6046,7 +6043,7 @@
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
       <c r="N9" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -6054,10 +6051,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>313</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>314</v>
       </c>
       <c r="D10" s="43"/>
       <c r="E10" s="43"/>
@@ -6070,7 +6067,7 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -6078,10 +6075,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>315</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>316</v>
       </c>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
@@ -6094,7 +6091,7 @@
       <c r="L11" s="43"/>
       <c r="M11" s="43"/>
       <c r="N11" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -6102,10 +6099,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="C12" s="43" t="s">
         <v>317</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>318</v>
       </c>
       <c r="D12" s="43"/>
       <c r="E12" s="43"/>
@@ -6118,7 +6115,7 @@
       <c r="L12" s="43"/>
       <c r="M12" s="43"/>
       <c r="N12" s="45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -6126,10 +6123,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>320</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>321</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
@@ -6142,12 +6139,12 @@
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
       <c r="N13" s="47" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6166,49 +6163,49 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="J16" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="L16" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>337</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -6973,12 +6970,12 @@
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7028,17 +7025,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7050,14 +7047,14 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="47">
         <v>30</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
@@ -7066,14 +7063,14 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="47">
         <v>25</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="43"/>
@@ -7082,14 +7079,14 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="47">
         <v>25</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E7" s="43"/>
       <c r="F7" s="43"/>
@@ -7098,14 +7095,14 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="47">
         <v>20</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E8" s="43"/>
       <c r="F8" s="43"/>
@@ -7114,7 +7111,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -7126,7 +7123,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B11" s="50"/>
       <c r="C11" s="50"/>
@@ -7138,7 +7135,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -7150,22 +7147,22 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="E14" s="51" t="s">
         <v>357</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>358</v>
       </c>
       <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15" s="52" t="s">
         <v>2</v>
@@ -7174,7 +7171,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F15" s="52">
         <v>37</v>
@@ -7182,7 +7179,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B16" s="52" t="s">
         <v>3</v>
@@ -7191,7 +7188,7 @@
         <v>350</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F16" s="52">
         <v>36</v>
@@ -7199,7 +7196,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="52" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B17" s="52" t="s">
         <v>4</v>
@@ -7208,7 +7205,7 @@
         <v>350</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F17" s="52">
         <v>24</v>
@@ -7216,7 +7213,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B18" s="52" t="s">
         <v>5</v>
@@ -7225,7 +7222,7 @@
         <v>250</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F18" s="52">
         <v>15</v>
@@ -7233,7 +7230,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="52" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B19" s="52" t="s">
         <v>6</v>
@@ -7242,7 +7239,7 @@
         <v>150</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F19" s="52">
         <v>14</v>
@@ -7250,7 +7247,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B20" s="52" t="s">
         <v>7</v>
@@ -7259,7 +7256,7 @@
         <v>100</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F20" s="52">
         <v>12</v>
@@ -7267,13 +7264,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C21" s="47">
         <v>1400</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F21" s="52">
         <v>11</v>
@@ -7281,7 +7278,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="49" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F22" s="52">
         <v>11</v>
@@ -7289,7 +7286,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F23" s="52">
         <v>10</v>
@@ -7297,7 +7294,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="49" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F24" s="52">
         <v>10</v>
@@ -7305,7 +7302,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F25" s="52">
         <v>10</v>
@@ -7313,7 +7310,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F26" s="52">
         <v>5</v>
@@ -7321,7 +7318,7 @@
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F27" s="52">
         <v>5</v>
@@ -7329,7 +7326,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -7341,28 +7338,28 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="D31" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="F31" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G31" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>385</v>
-      </c>
       <c r="H31" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -7370,19 +7367,19 @@
         <v>1</v>
       </c>
       <c r="B32" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="D32" s="55" t="s">
         <v>386</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>360</v>
-      </c>
-      <c r="D32" s="55" t="s">
-        <v>387</v>
       </c>
       <c r="E32" s="54">
         <v>257</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G32" s="54">
         <v>100</v>
@@ -7396,19 +7393,19 @@
         <v>2</v>
       </c>
       <c r="B33" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="D33" s="55" t="s">
         <v>389</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>362</v>
-      </c>
-      <c r="D33" s="55" t="s">
-        <v>390</v>
       </c>
       <c r="E33" s="54">
         <v>200</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G33" s="54">
         <v>95</v>
@@ -7422,19 +7419,19 @@
         <v>3</v>
       </c>
       <c r="B34" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="D34" s="55" t="s">
         <v>391</v>
-      </c>
-      <c r="C34" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="D34" s="55" t="s">
-        <v>392</v>
       </c>
       <c r="E34" s="54">
         <v>200</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G34" s="54">
         <v>77</v>
@@ -7448,19 +7445,19 @@
         <v>4</v>
       </c>
       <c r="B35" s="55" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E35" s="54">
         <v>2716</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G35" s="54">
         <v>95</v>
@@ -7474,19 +7471,19 @@
         <v>5</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E36" s="54">
         <v>150</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G36" s="54">
         <v>95</v>
@@ -7500,19 +7497,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C37" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E37" s="54">
         <v>190</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G37" s="54">
         <v>80</v>
@@ -7526,19 +7523,19 @@
         <v>7</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E38" s="54">
         <v>150</v>
       </c>
       <c r="F38" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G38" s="54">
         <v>80</v>
@@ -7552,19 +7549,19 @@
         <v>8</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E39" s="54">
         <v>2170</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G39" s="54">
         <v>95</v>
@@ -7578,19 +7575,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E40" s="54">
         <v>22</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G40" s="54">
         <v>77</v>
@@ -7604,19 +7601,19 @@
         <v>10</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E41" s="54">
         <v>140</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G41" s="54">
         <v>95</v>
@@ -7630,19 +7627,19 @@
         <v>11</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E42" s="54">
         <v>60</v>
       </c>
       <c r="F42" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G42" s="54">
         <v>73</v>
@@ -7656,19 +7653,19 @@
         <v>12</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E43" s="54">
         <v>54</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G43" s="54">
         <v>73</v>
@@ -7682,19 +7679,19 @@
         <v>13</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C44" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E44" s="54">
         <v>39</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G44" s="54">
         <v>68</v>
@@ -7708,19 +7705,19 @@
         <v>14</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D45" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E45" s="54">
         <v>108</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G45" s="54">
         <v>77</v>
@@ -7734,19 +7731,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="55" t="s">
+        <v>403</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>374</v>
+      </c>
+      <c r="D46" s="55" t="s">
         <v>404</v>
-      </c>
-      <c r="C46" s="54" t="s">
-        <v>375</v>
-      </c>
-      <c r="D46" s="55" t="s">
-        <v>405</v>
       </c>
       <c r="E46" s="54">
         <v>60</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G46" s="54">
         <v>67</v>
@@ -7760,19 +7757,19 @@
         <v>16</v>
       </c>
       <c r="B47" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D47" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E47" s="54">
         <v>80</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G47" s="54">
         <v>72</v>
@@ -7786,19 +7783,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C48" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E48" s="54">
         <v>200</v>
       </c>
       <c r="F48" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G48" s="54">
         <v>95</v>
@@ -7812,19 +7809,19 @@
         <v>18</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D49" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E49" s="54">
         <v>125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G49" s="54">
         <v>95</v>
@@ -7838,19 +7835,19 @@
         <v>19</v>
       </c>
       <c r="B50" s="55" t="s">
+        <v>408</v>
+      </c>
+      <c r="C50" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="D50" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E50" s="54" t="s">
         <v>409</v>
       </c>
-      <c r="C50" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="D50" s="55" t="s">
+      <c r="F50" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E50" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F50" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G50" s="54">
         <v>77</v>
@@ -7864,19 +7861,19 @@
         <v>20</v>
       </c>
       <c r="B51" s="55" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D51" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E51" s="54">
         <v>200</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G51" s="54">
         <v>75</v>
@@ -7890,19 +7887,19 @@
         <v>21</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E52" s="54">
         <v>165</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G52" s="54">
         <v>95</v>
@@ -7916,19 +7913,19 @@
         <v>22</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E53" s="54">
         <v>70</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G53" s="54">
         <v>75</v>
@@ -7942,19 +7939,19 @@
         <v>23</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E54" s="54">
         <v>100</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G54" s="54">
         <v>95</v>
@@ -7968,19 +7965,19 @@
         <v>24</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E55" s="54">
         <v>158</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G55" s="54">
         <v>95</v>
@@ -7994,19 +7991,19 @@
         <v>25</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D56" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E56" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F56" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E56" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F56" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G56" s="54">
         <v>77</v>
@@ -8020,19 +8017,19 @@
         <v>26</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E57" s="54">
         <v>96</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G57" s="54">
         <v>90</v>
@@ -8046,19 +8043,19 @@
         <v>27</v>
       </c>
       <c r="B58" s="55" t="s">
+        <v>416</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>369</v>
+      </c>
+      <c r="D58" s="55" t="s">
         <v>417</v>
-      </c>
-      <c r="C58" s="54" t="s">
-        <v>370</v>
-      </c>
-      <c r="D58" s="55" t="s">
-        <v>418</v>
       </c>
       <c r="E58" s="54">
         <v>120</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G58" s="54">
         <v>68</v>
@@ -8072,19 +8069,19 @@
         <v>28</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E59" s="54">
         <v>41</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G59" s="54">
         <v>68</v>
@@ -8098,19 +8095,19 @@
         <v>29</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C60" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D60" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E60" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F60" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E60" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F60" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G60" s="54">
         <v>68</v>
@@ -8124,19 +8121,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C61" s="54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D61" s="55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E61" s="54">
         <v>40</v>
       </c>
       <c r="F61" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G61" s="54">
         <v>69</v>
@@ -8150,19 +8147,19 @@
         <v>31</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C62" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D62" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E62" s="54">
         <v>67</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G62" s="54">
         <v>72</v>
@@ -8176,19 +8173,19 @@
         <v>32</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E63" s="54">
         <v>60</v>
       </c>
       <c r="F63" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G63" s="54">
         <v>67</v>
@@ -8202,19 +8199,19 @@
         <v>33</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C64" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E64" s="54">
         <v>150</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G64" s="54">
         <v>95</v>
@@ -8228,19 +8225,19 @@
         <v>34</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E65" s="54">
         <v>89</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G65" s="54">
         <v>90</v>
@@ -8254,19 +8251,19 @@
         <v>35</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D66" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E66" s="54">
         <v>57</v>
       </c>
       <c r="F66" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G66" s="54">
         <v>63</v>
@@ -8280,19 +8277,19 @@
         <v>36</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C67" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E67" s="54">
         <v>54</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G67" s="54">
         <v>75</v>
@@ -8306,19 +8303,19 @@
         <v>37</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C68" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E68" s="54">
         <v>80</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G68" s="54">
         <v>72</v>
@@ -8332,19 +8329,19 @@
         <v>38</v>
       </c>
       <c r="B69" s="55" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C69" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D69" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E69" s="54">
         <v>200</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G69" s="54">
         <v>72</v>
@@ -8358,19 +8355,19 @@
         <v>39</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C70" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D70" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E70" s="54">
         <v>1000</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G70" s="54">
         <v>70</v>
@@ -8384,19 +8381,19 @@
         <v>40</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D71" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E71" s="54">
         <v>120</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G71" s="54">
         <v>95</v>
@@ -8410,19 +8407,19 @@
         <v>41</v>
       </c>
       <c r="B72" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C72" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D72" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E72" s="54">
         <v>83</v>
       </c>
       <c r="F72" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G72" s="54">
         <v>90</v>
@@ -8436,19 +8433,19 @@
         <v>42</v>
       </c>
       <c r="B73" s="55" t="s">
+        <v>433</v>
+      </c>
+      <c r="C73" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="D73" s="55" t="s">
         <v>434</v>
-      </c>
-      <c r="C73" s="54" t="s">
-        <v>360</v>
-      </c>
-      <c r="D73" s="55" t="s">
-        <v>435</v>
       </c>
       <c r="E73" s="54">
         <v>120</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G73" s="54">
         <v>95</v>
@@ -8462,19 +8459,19 @@
         <v>43</v>
       </c>
       <c r="B74" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C74" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D74" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E74" s="54">
         <v>50</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G74" s="54">
         <v>72</v>
@@ -8488,19 +8485,19 @@
         <v>44</v>
       </c>
       <c r="B75" s="55" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C75" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D75" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E75" s="54">
         <v>80</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G75" s="54">
         <v>90</v>
@@ -8514,19 +8511,19 @@
         <v>45</v>
       </c>
       <c r="B76" s="55" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C76" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D76" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E76" s="54">
         <v>49</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G76" s="54">
         <v>68</v>
@@ -8540,19 +8537,19 @@
         <v>46</v>
       </c>
       <c r="B77" s="55" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C77" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D77" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E77" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F77" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E77" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F77" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G77" s="54">
         <v>68</v>
@@ -8566,19 +8563,19 @@
         <v>47</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C78" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E78" s="54">
         <v>200</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G78" s="54">
         <v>70</v>
@@ -8592,19 +8589,19 @@
         <v>48</v>
       </c>
       <c r="B79" s="55" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C79" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D79" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E79" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G79" s="54">
         <v>63</v>
@@ -8618,19 +8615,19 @@
         <v>49</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C80" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E80" s="54">
         <v>120</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G80" s="54">
         <v>95</v>
@@ -8644,19 +8641,19 @@
         <v>50</v>
       </c>
       <c r="B81" s="55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C81" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D81" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E81" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F81" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E81" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F81" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G81" s="54">
         <v>70</v>
@@ -8670,19 +8667,19 @@
         <v>51</v>
       </c>
       <c r="B82" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C82" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E82" s="54">
         <v>80</v>
       </c>
       <c r="F82" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G82" s="54">
         <v>90</v>
@@ -8696,19 +8693,19 @@
         <v>52</v>
       </c>
       <c r="B83" s="55" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C83" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D83" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E83" s="54">
         <v>67</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G83" s="54">
         <v>72</v>
@@ -8722,19 +8719,19 @@
         <v>53</v>
       </c>
       <c r="B84" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C84" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D84" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E84" s="54">
         <v>36</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G84" s="54">
         <v>67</v>
@@ -8748,19 +8745,19 @@
         <v>54</v>
       </c>
       <c r="B85" s="55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C85" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D85" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E85" s="54">
         <v>11</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G85" s="54">
         <v>72</v>
@@ -8774,19 +8771,19 @@
         <v>55</v>
       </c>
       <c r="B86" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C86" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D86" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E86" s="54">
         <v>110</v>
       </c>
       <c r="F86" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G86" s="54">
         <v>95</v>
@@ -8800,19 +8797,19 @@
         <v>56</v>
       </c>
       <c r="B87" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C87" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D87" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E87" s="54">
         <v>80</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G87" s="54">
         <v>72</v>
@@ -8826,19 +8823,19 @@
         <v>57</v>
       </c>
       <c r="B88" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C88" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D88" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E88" s="54">
         <v>70</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G88" s="54">
         <v>90</v>
@@ -8852,19 +8849,19 @@
         <v>58</v>
       </c>
       <c r="B89" s="55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C89" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D89" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E89" s="54">
         <v>107</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G89" s="54">
         <v>95</v>
@@ -8878,19 +8875,19 @@
         <v>59</v>
       </c>
       <c r="B90" s="55" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C90" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D90" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E90" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F90" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G90" s="54">
         <v>72</v>
@@ -8904,19 +8901,19 @@
         <v>60</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C91" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D91" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E91" s="54">
         <v>70</v>
       </c>
       <c r="F91" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G91" s="54">
         <v>65</v>
@@ -8930,19 +8927,19 @@
         <v>61</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C92" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D92" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E92" s="54">
         <v>62</v>
       </c>
       <c r="F92" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G92" s="54">
         <v>90</v>
@@ -8956,19 +8953,19 @@
         <v>62</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C93" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D93" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E93" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F93" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E93" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F93" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G93" s="54">
         <v>68</v>
@@ -8982,19 +8979,19 @@
         <v>63</v>
       </c>
       <c r="B94" s="55" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C94" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D94" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E94" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F94" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E94" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F94" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G94" s="54">
         <v>68</v>
@@ -9008,19 +9005,19 @@
         <v>64</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C95" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D95" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="E95" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="F95" s="54" t="s">
         <v>387</v>
-      </c>
-      <c r="E95" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="F95" s="54" t="s">
-        <v>388</v>
       </c>
       <c r="G95" s="54">
         <v>70</v>
@@ -9034,19 +9031,19 @@
         <v>65</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C96" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E96" s="54">
         <v>100</v>
       </c>
       <c r="F96" s="54" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G96" s="54">
         <v>95</v>
@@ -9060,19 +9057,19 @@
         <v>66</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C97" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E97" s="54">
         <v>60</v>
       </c>
       <c r="F97" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G97" s="54">
         <v>90</v>
@@ -9086,19 +9083,19 @@
         <v>67</v>
       </c>
       <c r="B98" s="55" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C98" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E98" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F98" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G98" s="54">
         <v>63</v>
@@ -9112,19 +9109,19 @@
         <v>68</v>
       </c>
       <c r="B99" s="55" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C99" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E99" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F99" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G99" s="54">
         <v>72</v>
@@ -9138,19 +9135,19 @@
         <v>69</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C100" s="54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E100" s="54">
         <v>40</v>
       </c>
       <c r="F100" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G100" s="54">
         <v>64</v>
@@ -9164,19 +9161,19 @@
         <v>70</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C101" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E101" s="54">
         <v>67</v>
       </c>
       <c r="F101" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G101" s="54">
         <v>72</v>
@@ -9190,19 +9187,19 @@
         <v>71</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C102" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E102" s="54">
         <v>70</v>
       </c>
       <c r="F102" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G102" s="54">
         <v>62</v>
@@ -9216,19 +9213,19 @@
         <v>72</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C103" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D103" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E103" s="54">
         <v>100</v>
       </c>
       <c r="F103" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G103" s="54">
         <v>95</v>
@@ -9242,19 +9239,19 @@
         <v>73</v>
       </c>
       <c r="B104" s="55" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C104" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D104" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E104" s="54">
         <v>55</v>
       </c>
       <c r="F104" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G104" s="54">
         <v>90</v>
@@ -9268,19 +9265,19 @@
         <v>74</v>
       </c>
       <c r="B105" s="55" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C105" s="54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D105" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E105" s="54">
         <v>57</v>
       </c>
       <c r="F105" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G105" s="54">
         <v>63</v>
@@ -9294,19 +9291,19 @@
         <v>75</v>
       </c>
       <c r="B106" s="55" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C106" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D106" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E106" s="54">
         <v>40</v>
       </c>
       <c r="F106" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G106" s="54">
         <v>65</v>
@@ -9320,19 +9317,19 @@
         <v>76</v>
       </c>
       <c r="B107" s="55" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C107" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D107" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E107" s="54">
         <v>80</v>
       </c>
       <c r="F107" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G107" s="54">
         <v>72</v>
@@ -9346,19 +9343,19 @@
         <v>77</v>
       </c>
       <c r="B108" s="55" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C108" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D108" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E108" s="54">
         <v>100</v>
       </c>
       <c r="F108" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G108" s="54">
         <v>95</v>
@@ -9372,19 +9369,19 @@
         <v>78</v>
       </c>
       <c r="B109" s="55" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C109" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D109" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E109" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F109" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G109" s="54">
         <v>72</v>
@@ -9398,19 +9395,19 @@
         <v>79</v>
       </c>
       <c r="B110" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C110" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D110" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E110" s="54">
         <v>66</v>
       </c>
       <c r="F110" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G110" s="54">
         <v>65</v>
@@ -9424,19 +9421,19 @@
         <v>80</v>
       </c>
       <c r="B111" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C111" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D111" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E111" s="54">
         <v>54</v>
       </c>
       <c r="F111" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G111" s="54">
         <v>90</v>
@@ -9450,19 +9447,19 @@
         <v>81</v>
       </c>
       <c r="B112" s="55" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C112" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D112" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E112" s="54">
         <v>7</v>
       </c>
       <c r="F112" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G112" s="54">
         <v>63</v>
@@ -9476,19 +9473,19 @@
         <v>82</v>
       </c>
       <c r="B113" s="55" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C113" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D113" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E113" s="54">
         <v>1</v>
       </c>
       <c r="F113" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G113" s="54">
         <v>63</v>
@@ -9502,19 +9499,19 @@
         <v>83</v>
       </c>
       <c r="B114" s="55" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C114" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D114" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E114" s="54">
         <v>300</v>
       </c>
       <c r="F114" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G114" s="54">
         <v>90</v>
@@ -9528,19 +9525,19 @@
         <v>84</v>
       </c>
       <c r="B115" s="55" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C115" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D115" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E115" s="54">
         <v>50</v>
       </c>
       <c r="F115" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G115" s="54">
         <v>90</v>
@@ -9554,19 +9551,19 @@
         <v>85</v>
       </c>
       <c r="B116" s="55" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C116" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D116" s="55" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E116" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F116" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G116" s="54">
         <v>72</v>
@@ -9580,19 +9577,19 @@
         <v>86</v>
       </c>
       <c r="B117" s="55" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C117" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D117" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E117" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F117" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G117" s="54">
         <v>63</v>
@@ -9606,19 +9603,19 @@
         <v>87</v>
       </c>
       <c r="B118" s="55" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C118" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D118" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E118" s="54">
         <v>250</v>
       </c>
       <c r="F118" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G118" s="54">
         <v>90</v>
@@ -9632,19 +9629,19 @@
         <v>88</v>
       </c>
       <c r="B119" s="55" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C119" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D119" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E119" s="54">
         <v>12</v>
       </c>
       <c r="F119" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G119" s="54">
         <v>65</v>
@@ -9658,19 +9655,19 @@
         <v>89</v>
       </c>
       <c r="B120" s="55" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C120" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D120" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E120" s="54">
         <v>67</v>
       </c>
       <c r="F120" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G120" s="54">
         <v>72</v>
@@ -9684,19 +9681,19 @@
         <v>90</v>
       </c>
       <c r="B121" s="55" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C121" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D121" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E121" s="54">
         <v>15</v>
       </c>
       <c r="F121" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G121" s="54">
         <v>62</v>
@@ -9710,19 +9707,19 @@
         <v>91</v>
       </c>
       <c r="B122" s="55" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C122" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D122" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E122" s="54">
         <v>50</v>
       </c>
       <c r="F122" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G122" s="54">
         <v>90</v>
@@ -9736,19 +9733,19 @@
         <v>92</v>
       </c>
       <c r="B123" s="55" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C123" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D123" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E123" s="54">
         <v>6</v>
       </c>
       <c r="F123" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G123" s="54">
         <v>65</v>
@@ -9762,19 +9759,19 @@
         <v>93</v>
       </c>
       <c r="B124" s="55" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C124" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D124" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E124" s="54">
         <v>200</v>
       </c>
       <c r="F124" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G124" s="54">
         <v>90</v>
@@ -9788,19 +9785,19 @@
         <v>94</v>
       </c>
       <c r="B125" s="55" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C125" s="54" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D125" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E125" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F125" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G125" s="54">
         <v>72</v>
@@ -9814,19 +9811,19 @@
         <v>95</v>
       </c>
       <c r="B126" s="55" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C126" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D126" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E126" s="54">
         <v>600</v>
       </c>
       <c r="F126" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G126" s="54">
         <v>85</v>
@@ -9840,19 +9837,19 @@
         <v>96</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C127" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D127" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E127" s="54">
         <v>5</v>
       </c>
       <c r="F127" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G127" s="54">
         <v>63</v>
@@ -9866,19 +9863,19 @@
         <v>97</v>
       </c>
       <c r="B128" s="55" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C128" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D128" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E128" s="54">
         <v>80</v>
       </c>
       <c r="F128" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G128" s="54">
         <v>72</v>
@@ -9892,19 +9889,19 @@
         <v>98</v>
       </c>
       <c r="B129" s="55" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C129" s="54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D129" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E129" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F129" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G129" s="54">
         <v>63</v>
@@ -9918,19 +9915,19 @@
         <v>99</v>
       </c>
       <c r="B130" s="55" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C130" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D130" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E130" s="54">
         <v>180</v>
       </c>
       <c r="F130" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G130" s="54">
         <v>90</v>
@@ -9944,19 +9941,19 @@
         <v>100</v>
       </c>
       <c r="B131" s="55" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C131" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D131" s="55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E131" s="54">
         <v>136</v>
       </c>
       <c r="F131" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G131" s="54">
         <v>85</v>
@@ -9997,7 +9994,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -10007,27 +10004,27 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -10037,17 +10034,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -10057,37 +10054,37 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -10097,22 +10094,22 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -10122,27 +10119,27 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -10152,17 +10149,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
+++ b/docs/models/ProofLoop_タスクシート_2026-08-07.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438194C9-BCCF-47E5-8C29-600E3EFEFF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859FC9F3-3492-4383-9A43-818B85CB438C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11115" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ガント" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="523">
   <si>
     <t>ProofLoop タスクシート 2026-08 → 2027-01（最終更新 2026-08-11）</t>
   </si>
@@ -1579,14 +1579,6 @@
   </si>
   <si>
     <t>・第1バッチ（B9）と企業打診 第1バッチ（C7）が出す実測値が最初の分岐点。9月頭に全体を組み替える前提で動く。</t>
-  </si>
-  <si>
-    <t>✅ 完了</t>
-    <phoneticPr fontId="33"/>
-  </si>
-  <si>
-    <t>✅ 完了</t>
-    <phoneticPr fontId="33"/>
   </si>
   <si>
     <t>進行中</t>
@@ -1595,6 +1587,9 @@
   <si>
     <t>未着手</t>
     <phoneticPr fontId="33"/>
+  </si>
+  <si>
+    <t>中止</t>
   </si>
 </sst>
 </file>
@@ -2098,11 +2093,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2714,8 +2709,8 @@
       <c r="H6" s="12">
         <v>1</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>521</v>
+      <c r="I6" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -2756,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>27</v>
+        <v>522</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
@@ -2796,8 +2791,8 @@
       <c r="H8" s="12">
         <v>2</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>522</v>
+      <c r="I8" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
@@ -2838,7 +2833,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -3657,8 +3652,8 @@
       <c r="H29" s="12">
         <v>2</v>
       </c>
-      <c r="I29" s="12" t="s">
-        <v>520</v>
+      <c r="I29" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
@@ -3698,8 +3693,8 @@
       <c r="H30" s="12">
         <v>2</v>
       </c>
-      <c r="I30" s="12" t="s">
-        <v>520</v>
+      <c r="I30" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
@@ -3739,8 +3734,8 @@
       <c r="H31" s="12">
         <v>3</v>
       </c>
-      <c r="I31" s="12" t="s">
-        <v>520</v>
+      <c r="I31" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
@@ -4764,8 +4759,8 @@
       <c r="H56" s="12">
         <v>2</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>520</v>
+      <c r="I56" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J56" s="13"/>
       <c r="K56" s="13"/>
@@ -4805,8 +4800,8 @@
       <c r="H57" s="12">
         <v>2</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>520</v>
+      <c r="I57" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="J57" s="13"/>
       <c r="K57" s="13"/>
@@ -5421,7 +5416,7 @@
         <v>4</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J72" s="13"/>
       <c r="K72" s="13"/>
@@ -5844,17 +5839,17 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="35" t="s">
@@ -5863,15 +5858,15 @@
       <c r="B14" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="35" t="s">
@@ -5880,15 +5875,15 @@
       <c r="B15" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="35" t="s">
@@ -5897,15 +5892,15 @@
       <c r="B16" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="50" t="s">
         <v>284</v>
       </c>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="35" t="s">
@@ -5914,15 +5909,15 @@
       <c r="B17" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="50" t="s">
         <v>287</v>
       </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="35" t="s">
@@ -5931,28 +5926,28 @@
       <c r="B18" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="50" t="s">
         <v>290</v>
       </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="52" t="s">
@@ -5991,17 +5986,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="C17:I17"/>
     <mergeCell ref="C18:I18"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:I22"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="C17:I17"/>
   </mergeCells>
   <phoneticPr fontId="33"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6039,23 +6034,23 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="35">
@@ -6274,23 +6269,23 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="51"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
@@ -7111,17 +7106,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="C5:M5"/>
+    <mergeCell ref="C6:M6"/>
+    <mergeCell ref="C7:M7"/>
+    <mergeCell ref="C8:M8"/>
     <mergeCell ref="A15:O15"/>
     <mergeCell ref="C9:M9"/>
     <mergeCell ref="C10:M10"/>
     <mergeCell ref="C11:M11"/>
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="C13:M13"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="C5:M5"/>
-    <mergeCell ref="C6:M6"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="C8:M8"/>
   </mergeCells>
   <phoneticPr fontId="33"/>
   <dataValidations count="3">
@@ -7166,16 +7161,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="52" t="s">
@@ -7242,16 +7237,16 @@
       <c r="H8" s="54"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="51" t="s">
         <v>351</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="56" t="s">
@@ -7457,16 +7452,16 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="51" t="s">
         <v>378</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
@@ -10096,6 +10091,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:H6"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="E14:F14"/>
@@ -10105,11 +10105,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:H6"/>
   </mergeCells>
   <phoneticPr fontId="33"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
